--- a/EGY_WB_timeseries.xlsx
+++ b/EGY_WB_timeseries.xlsx
@@ -14,21 +14,111 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+  <si>
+    <t>Bank liquid reserves to bank assets (%)</t>
+  </si>
+  <si>
+    <t>Control of Corruption</t>
+  </si>
+  <si>
+    <t>Current account balance (% of GDP)</t>
+  </si>
+  <si>
+    <t>Debt (% of GDP)</t>
+  </si>
+  <si>
+    <t>Domestic credit to private sector (% of GDP)</t>
+  </si>
+  <si>
+    <t>Exports of goods and services (% of GDP)</t>
+  </si>
+  <si>
+    <t>External debt stocks (% of GNI)</t>
+  </si>
+  <si>
+    <t>External debt stocks (current US$)</t>
+  </si>
   <si>
     <t>GDP growth (annual %)</t>
   </si>
   <si>
+    <t>GDP per capita (PPP, international $)</t>
+  </si>
+  <si>
+    <t>GDP per capita (current US$)</t>
+  </si>
+  <si>
+    <t>GDP per capita growth (annual %)</t>
+  </si>
+  <si>
+    <t>Gini index</t>
+  </si>
+  <si>
+    <t>Government Effectiveness</t>
+  </si>
+  <si>
+    <t>Government consumption (% of GDP)</t>
+  </si>
+  <si>
+    <t>Government expenditure (% of GDP)</t>
+  </si>
+  <si>
+    <t>Government revenue (% of GDP)</t>
+  </si>
+  <si>
+    <t>Imports of goods and services (% of GDP)</t>
+  </si>
+  <si>
     <t>Inflation, consumer prices (annual %)</t>
   </si>
   <si>
     <t>Interest payments (% of GDP)</t>
   </si>
   <si>
+    <t>Life expectancy at birth (years)</t>
+  </si>
+  <si>
+    <t>Military expenditure (% of GDP)</t>
+  </si>
+  <si>
+    <t>Net lending/borrowing (% of GDP)</t>
+  </si>
+  <si>
+    <t>Political Stability and Absence of Violence</t>
+  </si>
+  <si>
+    <t>Population, total</t>
+  </si>
+  <si>
+    <t>Poverty headcount ratio ($2.15/day)</t>
+  </si>
+  <si>
+    <t>Regulatory Quality</t>
+  </si>
+  <si>
+    <t>Rule of Law</t>
+  </si>
+  <si>
     <t>Tax revenue (% of GDP)</t>
   </si>
   <si>
+    <t>Total reserves (current US$)</t>
+  </si>
+  <si>
+    <t>Total reserves (months of imports)</t>
+  </si>
+  <si>
+    <t>Trade openness (% of GDP)</t>
+  </si>
+  <si>
     <t>Unemployment (% labor force)</t>
+  </si>
+  <si>
+    <t>Urban population (% of total)</t>
+  </si>
+  <si>
+    <t>Voice and Accountability</t>
   </si>
   <si>
     <t>date</t>
@@ -389,12 +479,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:AJ26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:36">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -411,406 +501,2422 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:36">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
-      <c r="B2">
+      <c r="C2">
+        <v>-0.4926677942276</v>
+      </c>
+      <c r="D2">
+        <v>-0.9725702734489859</v>
+      </c>
+      <c r="F2">
+        <v>51.9532784475154</v>
+      </c>
+      <c r="G2">
+        <v>16.2011173184358</v>
+      </c>
+      <c r="H2">
+        <v>29.1436697781484</v>
+      </c>
+      <c r="I2">
+        <v>29232716500.9</v>
+      </c>
+      <c r="J2">
         <v>6.37000382991766</v>
       </c>
-      <c r="F2">
+      <c r="K2">
+        <v>5451.51566992118</v>
+      </c>
+      <c r="L2">
+        <v>1366.09274372613</v>
+      </c>
+      <c r="M2">
+        <v>4.09609057659976</v>
+      </c>
+      <c r="O2">
+        <v>-0.174759328365326</v>
+      </c>
+      <c r="P2">
+        <v>11.2025874742723</v>
+      </c>
+      <c r="S2">
+        <v>22.8168185827698</v>
+      </c>
+      <c r="V2">
+        <v>67.33199999999999</v>
+      </c>
+      <c r="W2">
+        <v>2.55126513982739</v>
+      </c>
+      <c r="Y2">
+        <v>0.0497975237667561</v>
+      </c>
+      <c r="Z2">
+        <v>73083284</v>
+      </c>
+      <c r="AB2">
+        <v>-0.301753908395767</v>
+      </c>
+      <c r="AC2">
+        <v>-0.0515826977789402</v>
+      </c>
+      <c r="AE2">
+        <v>13785040867.624</v>
+      </c>
+      <c r="AF2">
+        <v>6.92773642731755</v>
+      </c>
+      <c r="AG2">
+        <v>39.0179359012055</v>
+      </c>
+      <c r="AH2">
         <v>8.98</v>
       </c>
+      <c r="AI2">
+        <v>42.797</v>
+      </c>
+      <c r="AJ2">
+        <v>-0.89450615644455</v>
+      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:36">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
       <c r="B3">
+        <v>22.607614704088</v>
+      </c>
+      <c r="D3">
+        <v>-0.401718427655422</v>
+      </c>
+      <c r="F3">
+        <v>54.9311402286033</v>
+      </c>
+      <c r="G3">
+        <v>17.4797881237803</v>
+      </c>
+      <c r="H3">
+        <v>28.9819896399422</v>
+      </c>
+      <c r="I3">
+        <v>28331673242.3</v>
+      </c>
+      <c r="J3">
         <v>3.53525197391507</v>
       </c>
-      <c r="F3">
+      <c r="K3">
+        <v>5650.05196237607</v>
+      </c>
+      <c r="L3">
+        <v>1295.1374184163</v>
+      </c>
+      <c r="M3">
+        <v>1.35955211640928</v>
+      </c>
+      <c r="P3">
+        <v>11.318650683022</v>
+      </c>
+      <c r="S3">
+        <v>22.330638416504</v>
+      </c>
+      <c r="V3">
+        <v>67.61199999999999</v>
+      </c>
+      <c r="W3">
+        <v>2.98556856033807</v>
+      </c>
+      <c r="Z3">
+        <v>74652029</v>
+      </c>
+      <c r="AE3">
+        <v>13598234040.4969</v>
+      </c>
+      <c r="AF3">
+        <v>7.45748900818796</v>
+      </c>
+      <c r="AG3">
+        <v>39.8104265402844</v>
+      </c>
+      <c r="AH3">
         <v>9.26</v>
       </c>
+      <c r="AI3">
+        <v>42.843</v>
+      </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:36">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
       <c r="B4">
+        <v>21.868495456407</v>
+      </c>
+      <c r="C4">
+        <v>-0.44015771150589</v>
+      </c>
+      <c r="D4">
+        <v>0.730979150171549</v>
+      </c>
+      <c r="F4">
+        <v>54.6553972024281</v>
+      </c>
+      <c r="G4">
+        <v>18.3161784111903</v>
+      </c>
+      <c r="H4">
+        <v>34.8088896707165</v>
+      </c>
+      <c r="I4">
+        <v>29671747582</v>
+      </c>
+      <c r="J4">
         <v>2.39020402573726</v>
       </c>
-      <c r="D4">
+      <c r="K4">
+        <v>5752.69708070468</v>
+      </c>
+      <c r="L4">
+        <v>1116.82884626213</v>
+      </c>
+      <c r="M4">
+        <v>0.258696268364815</v>
+      </c>
+      <c r="O4">
+        <v>-0.446098297834396</v>
+      </c>
+      <c r="P4">
+        <v>12.5890736342043</v>
+      </c>
+      <c r="Q4">
+        <v>27.2483504882555</v>
+      </c>
+      <c r="R4">
+        <v>24.349696489839</v>
+      </c>
+      <c r="S4">
+        <v>22.6708894167326</v>
+      </c>
+      <c r="U4">
         <v>19.665065282244</v>
       </c>
-      <c r="E4">
+      <c r="V4">
+        <v>67.846</v>
+      </c>
+      <c r="W4">
+        <v>3.27845479650374</v>
+      </c>
+      <c r="X4">
+        <v>-6.74531538664555</v>
+      </c>
+      <c r="Y4">
+        <v>-0.414172112941742</v>
+      </c>
+      <c r="Z4">
+        <v>76239137</v>
+      </c>
+      <c r="AB4">
+        <v>-0.456903666257858</v>
+      </c>
+      <c r="AC4">
+        <v>-0.0114680724218488</v>
+      </c>
+      <c r="AD4">
         <v>13.4077593032462</v>
       </c>
-      <c r="F4">
+      <c r="AE4">
+        <v>14076054422.998</v>
+      </c>
+      <c r="AF4">
+        <v>8.250266346708729</v>
+      </c>
+      <c r="AG4">
+        <v>40.9870678279229</v>
+      </c>
+      <c r="AH4">
         <v>10.01</v>
       </c>
+      <c r="AI4">
+        <v>42.889</v>
+      </c>
+      <c r="AJ4">
+        <v>-1.10229003429413</v>
+      </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:36">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
       <c r="B5">
+        <v>32.1374256238714</v>
+      </c>
+      <c r="C5">
+        <v>-0.530747950077057</v>
+      </c>
+      <c r="D5">
+        <v>4.66231377245509</v>
+      </c>
+      <c r="F5">
+        <v>53.897628742515</v>
+      </c>
+      <c r="G5">
+        <v>21.7964071856287</v>
+      </c>
+      <c r="H5">
+        <v>37.9984128219101</v>
+      </c>
+      <c r="I5">
+        <v>30467606765.2</v>
+      </c>
+      <c r="J5">
         <v>3.19345473739745</v>
       </c>
-      <c r="D5">
+      <c r="K5">
+        <v>5928.07945344715</v>
+      </c>
+      <c r="L5">
+        <v>1031.27556291284</v>
+      </c>
+      <c r="M5">
+        <v>1.05358246778609</v>
+      </c>
+      <c r="O5">
+        <v>-0.389788568019867</v>
+      </c>
+      <c r="P5">
+        <v>12.6706586826347</v>
+      </c>
+      <c r="Q5">
+        <v>27.3324550898204</v>
+      </c>
+      <c r="R5">
+        <v>25.4311377245509</v>
+      </c>
+      <c r="S5">
+        <v>24.3832335329341</v>
+      </c>
+      <c r="U5">
         <v>20.7925477377687</v>
       </c>
-      <c r="E5">
+      <c r="V5">
+        <v>68.045</v>
+      </c>
+      <c r="W5">
+        <v>3.17728527009726</v>
+      </c>
+      <c r="X5">
+        <v>-5.8162874251497</v>
+      </c>
+      <c r="Y5">
+        <v>-0.640924513339996</v>
+      </c>
+      <c r="Z5">
+        <v>77853548</v>
+      </c>
+      <c r="AB5">
+        <v>-0.574796617031097</v>
+      </c>
+      <c r="AC5">
+        <v>-0.00235446891747415</v>
+      </c>
+      <c r="AD5">
         <v>13.3499401197605</v>
       </c>
-      <c r="F5">
+      <c r="AE5">
+        <v>14603576021.3741</v>
+      </c>
+      <c r="AF5">
+        <v>8.55089573372287</v>
+      </c>
+      <c r="AG5">
+        <v>46.1796407185629</v>
+      </c>
+      <c r="AH5">
         <v>10.91</v>
       </c>
+      <c r="AI5">
+        <v>42.935</v>
+      </c>
+      <c r="AJ5">
+        <v>-1.08318543434143</v>
+      </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:36">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
       <c r="B6">
+        <v>32.4463926349112</v>
+      </c>
+      <c r="C6">
+        <v>-0.5835057497024539</v>
+      </c>
+      <c r="D6">
+        <v>4.97788419534309</v>
+      </c>
+      <c r="F6">
+        <v>54.0429142798269</v>
+      </c>
+      <c r="G6">
+        <v>28.2299608489594</v>
+      </c>
+      <c r="H6">
+        <v>39.9656119503054</v>
+      </c>
+      <c r="I6">
+        <v>31403286339</v>
+      </c>
+      <c r="J6">
         <v>4.0920716112534</v>
       </c>
-      <c r="D6">
+      <c r="K6">
+        <v>6207.12492160943</v>
+      </c>
+      <c r="L6">
+        <v>991.255689145253</v>
+      </c>
+      <c r="M6">
+        <v>1.96524683873078</v>
+      </c>
+      <c r="N6">
+        <v>31.8</v>
+      </c>
+      <c r="O6">
+        <v>-0.278711497783661</v>
+      </c>
+      <c r="P6">
+        <v>12.7549969091284</v>
+      </c>
+      <c r="Q6">
+        <v>26.8903770863383</v>
+      </c>
+      <c r="R6">
+        <v>24.6404286008654</v>
+      </c>
+      <c r="S6">
+        <v>29.5899443643107</v>
+      </c>
+      <c r="U6">
         <v>21.0859853332209</v>
       </c>
-      <c r="E6">
+      <c r="V6">
+        <v>68.211</v>
+      </c>
+      <c r="W6">
+        <v>2.87753123653597</v>
+      </c>
+      <c r="X6">
+        <v>-5.61055017514939</v>
+      </c>
+      <c r="Y6">
+        <v>-0.822401702404022</v>
+      </c>
+      <c r="Z6">
+        <v>79477443</v>
+      </c>
+      <c r="AA6">
+        <v>4.1</v>
+      </c>
+      <c r="AB6">
+        <v>-0.56948184967041</v>
+      </c>
+      <c r="AC6">
+        <v>0.0133178951218724</v>
+      </c>
+      <c r="AD6">
         <v>13.8359777457243</v>
       </c>
-      <c r="F6">
+      <c r="AE6">
+        <v>15338514716.8958</v>
+      </c>
+      <c r="AF6">
+        <v>6.63684137548043</v>
+      </c>
+      <c r="AG6">
+        <v>57.8199052132701</v>
+      </c>
+      <c r="AH6">
         <v>10.32</v>
       </c>
+      <c r="AI6">
+        <v>42.981</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.947557926177979</v>
+      </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:36">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
       <c r="B7">
+        <v>33.3785449003527</v>
+      </c>
+      <c r="C7">
+        <v>-0.5394995212554931</v>
+      </c>
+      <c r="D7">
+        <v>2.34529559888579</v>
+      </c>
+      <c r="F7">
+        <v>51.1654340531105</v>
+      </c>
+      <c r="G7">
+        <v>30.3435468895079</v>
+      </c>
+      <c r="H7">
+        <v>34.2213422280108</v>
+      </c>
+      <c r="I7">
+        <v>30575696632.4</v>
+      </c>
+      <c r="J7">
         <v>4.47174447174434</v>
       </c>
-      <c r="D7">
+      <c r="K7">
+        <v>6554.12885095179</v>
+      </c>
+      <c r="L7">
+        <v>1105.53920713903</v>
+      </c>
+      <c r="M7">
+        <v>2.38032461797421</v>
+      </c>
+      <c r="O7">
+        <v>-0.399056732654572</v>
+      </c>
+      <c r="P7">
+        <v>12.7390900649954</v>
+      </c>
+      <c r="Q7">
+        <v>27.3888579387187</v>
+      </c>
+      <c r="R7">
+        <v>24.2916620241411</v>
+      </c>
+      <c r="S7">
+        <v>32.6090993500464</v>
+      </c>
+      <c r="U7">
         <v>20.2089647363532</v>
       </c>
-      <c r="E7">
+      <c r="V7">
+        <v>68.355</v>
+      </c>
+      <c r="W7">
+        <v>2.71422040657605</v>
+      </c>
+      <c r="X7">
+        <v>-6.44885793871866</v>
+      </c>
+      <c r="Y7">
+        <v>-0.629358649253845</v>
+      </c>
+      <c r="Z7">
+        <v>81101004</v>
+      </c>
+      <c r="AB7">
+        <v>-0.45302626490593</v>
+      </c>
+      <c r="AC7">
+        <v>-0.00122323480900377</v>
+      </c>
+      <c r="AD7">
         <v>14.068635097493</v>
       </c>
-      <c r="F7">
+      <c r="AE7">
+        <v>21856784928.5556</v>
+      </c>
+      <c r="AF7">
+        <v>7.32906037591457</v>
+      </c>
+      <c r="AG7">
+        <v>62.9526462395543</v>
+      </c>
+      <c r="AH7">
         <v>11.049</v>
       </c>
+      <c r="AI7">
+        <v>43.027</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.964780926704407</v>
+      </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:36">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
       <c r="B8">
+        <v>34.0460304221546</v>
+      </c>
+      <c r="C8">
+        <v>-0.737334072589874</v>
+      </c>
+      <c r="D8">
+        <v>2.45322162862231</v>
+      </c>
+      <c r="F8">
+        <v>49.2909797353084</v>
+      </c>
+      <c r="G8">
+        <v>29.9498138254816</v>
+      </c>
+      <c r="H8">
+        <v>28.7414925057896</v>
+      </c>
+      <c r="I8">
+        <v>31028391832.6</v>
+      </c>
+      <c r="J8">
         <v>6.84383819379117</v>
       </c>
-      <c r="D8">
+      <c r="K8">
+        <v>7079.02808456919</v>
+      </c>
+      <c r="L8">
+        <v>1298.97900203124</v>
+      </c>
+      <c r="M8">
+        <v>4.77751297935043</v>
+      </c>
+      <c r="O8">
+        <v>-0.49823722243309</v>
+      </c>
+      <c r="P8">
+        <v>12.2875182127246</v>
+      </c>
+      <c r="Q8">
+        <v>32.7636716852841</v>
+      </c>
+      <c r="R8">
+        <v>28.1389833252388</v>
+      </c>
+      <c r="S8">
+        <v>31.5687226809131</v>
+      </c>
+      <c r="U8">
         <v>17.2010542481219</v>
       </c>
-      <c r="E8">
+      <c r="V8">
+        <v>68.49299999999999</v>
+      </c>
+      <c r="W8">
+        <v>2.60621860261331</v>
+      </c>
+      <c r="X8">
+        <v>-7.1684960336733</v>
+      </c>
+      <c r="Y8">
+        <v>-0.837807655334473</v>
+      </c>
+      <c r="Z8">
+        <v>82700403</v>
+      </c>
+      <c r="AB8">
+        <v>-0.407716184854507</v>
+      </c>
+      <c r="AC8">
+        <v>-0.278967440128326</v>
+      </c>
+      <c r="AD8">
         <v>15.8295127084345</v>
       </c>
-      <c r="F8">
+      <c r="AE8">
+        <v>26006845068.1543</v>
+      </c>
+      <c r="AF8">
+        <v>7.36480504492886</v>
+      </c>
+      <c r="AG8">
+        <v>61.5185365063947</v>
+      </c>
+      <c r="AH8">
         <v>10.49</v>
       </c>
+      <c r="AI8">
+        <v>43.073</v>
+      </c>
+      <c r="AJ8">
+        <v>-1.19926512241364</v>
+      </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:36">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
       <c r="B9">
+        <v>44.8521598670517</v>
+      </c>
+      <c r="C9">
+        <v>-0.737870097160339</v>
+      </c>
+      <c r="D9">
+        <v>0.315552631578947</v>
+      </c>
+      <c r="E9">
+        <v>85.7885338345865</v>
+      </c>
+      <c r="F9">
+        <v>45.5152215665951</v>
+      </c>
+      <c r="G9">
+        <v>30.249731471536</v>
+      </c>
+      <c r="H9">
+        <v>26.2922867901955</v>
+      </c>
+      <c r="I9">
+        <v>34604548133.8</v>
+      </c>
+      <c r="J9">
         <v>7.08782742681038</v>
       </c>
-      <c r="D9">
+      <c r="K9">
+        <v>7640.57228597204</v>
+      </c>
+      <c r="L9">
+        <v>1547.74170735909</v>
+      </c>
+      <c r="M9">
+        <v>5.0854672784842</v>
+      </c>
+      <c r="O9">
+        <v>-0.374726384878159</v>
+      </c>
+      <c r="P9">
+        <v>11.3319011815252</v>
+      </c>
+      <c r="Q9">
+        <v>29.3352309344791</v>
+      </c>
+      <c r="R9">
+        <v>27.1170918367347</v>
+      </c>
+      <c r="S9">
+        <v>34.828141783029</v>
+      </c>
+      <c r="U9">
         <v>17.560305150653</v>
       </c>
-      <c r="E9">
+      <c r="V9">
+        <v>68.627</v>
+      </c>
+      <c r="W9">
+        <v>2.37963467509709</v>
+      </c>
+      <c r="X9">
+        <v>-4.55796186895811</v>
+      </c>
+      <c r="Y9">
+        <v>-0.552382111549377</v>
+      </c>
+      <c r="Z9">
+        <v>84276225</v>
+      </c>
+      <c r="AB9">
+        <v>-0.317137002944946</v>
+      </c>
+      <c r="AC9">
+        <v>-0.246213480830193</v>
+      </c>
+      <c r="AD9">
         <v>15.3498523093448</v>
       </c>
-      <c r="F9">
+      <c r="AE9">
+        <v>32214421786.3476</v>
+      </c>
+      <c r="AF9">
+        <v>6.95056522562452</v>
+      </c>
+      <c r="AG9">
+        <v>65.07787325456501</v>
+      </c>
+      <c r="AH9">
         <v>8.800000000000001</v>
       </c>
+      <c r="AI9">
+        <v>43.078</v>
+      </c>
+      <c r="AJ9">
+        <v>-1.16774547100067</v>
+      </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:36">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
       <c r="B10">
+        <v>36.5103194310957</v>
+      </c>
+      <c r="C10">
+        <v>-0.7659092545509339</v>
+      </c>
+      <c r="D10">
+        <v>-0.868821887213847</v>
+      </c>
+      <c r="F10">
+        <v>42.7975137803462</v>
+      </c>
+      <c r="G10">
+        <v>33.0429927414852</v>
+      </c>
+      <c r="H10">
+        <v>20.6637689686303</v>
+      </c>
+      <c r="I10">
+        <v>33925338196.5</v>
+      </c>
+      <c r="J10">
         <v>7.15628356605819</v>
       </c>
-      <c r="D10">
+      <c r="K10">
+        <v>8190.70913161</v>
+      </c>
+      <c r="L10">
+        <v>1896.21594269779</v>
+      </c>
+      <c r="M10">
+        <v>5.17381069878276</v>
+      </c>
+      <c r="N10">
+        <v>31.1</v>
+      </c>
+      <c r="O10">
+        <v>-0.380703538656235</v>
+      </c>
+      <c r="P10">
+        <v>10.8877721943049</v>
+      </c>
+      <c r="Q10">
+        <v>30.3182043551089</v>
+      </c>
+      <c r="R10">
+        <v>27.6239352317141</v>
+      </c>
+      <c r="S10">
+        <v>38.6376326074819</v>
+      </c>
+      <c r="U10">
         <v>15.0853305376009</v>
       </c>
-      <c r="E10">
+      <c r="V10">
+        <v>68.761</v>
+      </c>
+      <c r="W10">
+        <v>2.18078548537016</v>
+      </c>
+      <c r="X10">
+        <v>-6.36079061976549</v>
+      </c>
+      <c r="Y10">
+        <v>-0.510431706905365</v>
+      </c>
+      <c r="Z10">
+        <v>85864789</v>
+      </c>
+      <c r="AA10">
+        <v>3.7</v>
+      </c>
+      <c r="AB10">
+        <v>-0.201634988188744</v>
+      </c>
+      <c r="AC10">
+        <v>-0.129783600568771</v>
+      </c>
+      <c r="AD10">
         <v>15.3205248464545</v>
       </c>
-      <c r="F10">
+      <c r="AE10">
+        <v>34330505048.3926</v>
+      </c>
+      <c r="AF10">
+        <v>5.97060049450951</v>
+      </c>
+      <c r="AG10">
+        <v>71.6806253489671</v>
+      </c>
+      <c r="AH10">
         <v>8.516999999999999</v>
       </c>
+      <c r="AI10">
+        <v>43.058</v>
+      </c>
+      <c r="AJ10">
+        <v>-1.21223938465118</v>
+      </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:36">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
       <c r="B11">
+        <v>34.1605103809245</v>
+      </c>
+      <c r="C11">
+        <v>-0.464862793684006</v>
+      </c>
+      <c r="D11">
+        <v>-1.7707391095759</v>
+      </c>
+      <c r="F11">
+        <v>36.0927133507004</v>
+      </c>
+      <c r="G11">
+        <v>24.9568221070812</v>
+      </c>
+      <c r="H11">
+        <v>18.7094477594032</v>
+      </c>
+      <c r="I11">
+        <v>35417097883.9</v>
+      </c>
+      <c r="J11">
         <v>4.67359979952391</v>
       </c>
-      <c r="D11">
+      <c r="K11">
+        <v>8465.020524126619</v>
+      </c>
+      <c r="L11">
+        <v>2161.63964573927</v>
+      </c>
+      <c r="M11">
+        <v>2.7155259206418</v>
+      </c>
+      <c r="O11">
+        <v>-0.208088099956512</v>
+      </c>
+      <c r="P11">
+        <v>11.3509882939935</v>
+      </c>
+      <c r="Q11">
+        <v>30.0771253118403</v>
+      </c>
+      <c r="R11">
+        <v>26.9200729226636</v>
+      </c>
+      <c r="S11">
+        <v>31.596622529265</v>
+      </c>
+      <c r="U11">
         <v>13.958581501277</v>
       </c>
-      <c r="E11">
+      <c r="V11">
+        <v>68.91500000000001</v>
+      </c>
+      <c r="W11">
+        <v>2.03264504307225</v>
+      </c>
+      <c r="X11">
+        <v>-6.56296296296296</v>
+      </c>
+      <c r="Y11">
+        <v>-0.607227087020874</v>
+      </c>
+      <c r="Z11">
+        <v>87501636</v>
+      </c>
+      <c r="AB11">
+        <v>-0.17781800031662</v>
+      </c>
+      <c r="AC11">
+        <v>-0.0833449959754944</v>
+      </c>
+      <c r="AD11">
         <v>15.6613605833813</v>
       </c>
-      <c r="F11">
+      <c r="AE11">
+        <v>34896678266.342</v>
+      </c>
+      <c r="AF11">
+        <v>7.35827452765158</v>
+      </c>
+      <c r="AG11">
+        <v>56.5534446363462</v>
+      </c>
+      <c r="AH11">
         <v>9.087</v>
       </c>
+      <c r="AI11">
+        <v>43.039</v>
+      </c>
+      <c r="AJ11">
+        <v>-1.15747153759003</v>
+      </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:36">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
       <c r="B12">
+        <v>33.3083123961479</v>
+      </c>
+      <c r="C12">
+        <v>-0.596871852874756</v>
+      </c>
+      <c r="D12">
+        <v>-2.05668307641306</v>
+      </c>
+      <c r="F12">
+        <v>33.0722952214189</v>
+      </c>
+      <c r="G12">
+        <v>21.3492458146859</v>
+      </c>
+      <c r="H12">
+        <v>17.1484993453553</v>
+      </c>
+      <c r="I12">
+        <v>36803931990.1</v>
+      </c>
+      <c r="J12">
         <v>5.1472348575531</v>
       </c>
-      <c r="D12">
+      <c r="K12">
+        <v>8837.764500337031</v>
+      </c>
+      <c r="L12">
+        <v>2455.08194645282</v>
+      </c>
+      <c r="M12">
+        <v>3.14977851168294</v>
+      </c>
+      <c r="N12">
+        <v>30.2</v>
+      </c>
+      <c r="O12">
+        <v>-0.321309953927994</v>
+      </c>
+      <c r="P12">
+        <v>11.163600198906</v>
+      </c>
+      <c r="Q12">
+        <v>28.8602519476214</v>
+      </c>
+      <c r="R12">
+        <v>24.7838223106249</v>
+      </c>
+      <c r="S12">
+        <v>26.5871042599039</v>
+      </c>
+      <c r="U12">
         <v>17.8615837104332</v>
       </c>
-      <c r="E12">
+      <c r="V12">
+        <v>69.078</v>
+      </c>
+      <c r="W12">
+        <v>1.95296705174529</v>
+      </c>
+      <c r="X12">
+        <v>-7.73391347588264</v>
+      </c>
+      <c r="Y12">
+        <v>-0.898418307304382</v>
+      </c>
+      <c r="Z12">
+        <v>89196072</v>
+      </c>
+      <c r="AA12">
+        <v>1.5</v>
+      </c>
+      <c r="AB12">
+        <v>-0.147598043084145</v>
+      </c>
+      <c r="AC12">
+        <v>-0.174863860011101</v>
+      </c>
+      <c r="AD12">
         <v>14.1300762473065</v>
       </c>
-      <c r="F12">
+      <c r="AE12">
+        <v>37028506134.5559</v>
+      </c>
+      <c r="AF12">
+        <v>6.70121378987163</v>
+      </c>
+      <c r="AG12">
+        <v>47.9363500745898</v>
+      </c>
+      <c r="AH12">
         <v>8.757</v>
       </c>
+      <c r="AI12">
+        <v>43.019</v>
+      </c>
+      <c r="AJ12">
+        <v>-1.18803703784943</v>
+      </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:36">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
       <c r="B13">
+        <v>16.7618206272571</v>
+      </c>
+      <c r="C13">
+        <v>-0.633263945579529</v>
+      </c>
+      <c r="D13">
+        <v>-2.32378812632193</v>
+      </c>
+      <c r="F13">
+        <v>31.1549232899382</v>
+      </c>
+      <c r="G13">
+        <v>20.5674276128656</v>
+      </c>
+      <c r="H13">
+        <v>15.3121406993227</v>
+      </c>
+      <c r="I13">
+        <v>35208762810.6</v>
+      </c>
+      <c r="J13">
         <v>1.7645719489982</v>
       </c>
-      <c r="C13">
+      <c r="K13">
+        <v>8988.107818806529</v>
+      </c>
+      <c r="L13">
+        <v>2590.64384891965</v>
+      </c>
+      <c r="M13">
+        <v>-0.354646267702748</v>
+      </c>
+      <c r="O13">
+        <v>-0.440889060497284</v>
+      </c>
+      <c r="P13">
+        <v>11.4506600539713</v>
+      </c>
+      <c r="Q13">
+        <v>29.1899277952009</v>
+      </c>
+      <c r="R13">
+        <v>21.9307417402086</v>
+      </c>
+      <c r="S13">
+        <v>24.6882065494858</v>
+      </c>
+      <c r="T13">
         <v>10.0649259874818</v>
       </c>
-      <c r="D13">
+      <c r="U13">
         <v>19.0798082369558</v>
       </c>
-      <c r="E13">
+      <c r="V13">
+        <v>69.232</v>
+      </c>
+      <c r="W13">
+        <v>1.83702551137618</v>
+      </c>
+      <c r="X13">
+        <v>-10.0824593392167</v>
+      </c>
+      <c r="Y13">
+        <v>-1.43705701828003</v>
+      </c>
+      <c r="Z13">
+        <v>91093059</v>
+      </c>
+      <c r="AB13">
+        <v>-0.246938586235046</v>
+      </c>
+      <c r="AC13">
+        <v>-0.483893096446991</v>
+      </c>
+      <c r="AD13">
         <v>14.0086354022318</v>
       </c>
-      <c r="F13">
+      <c r="AE13">
+        <v>18637541110.4777</v>
+      </c>
+      <c r="AF13">
+        <v>3.28531568230903</v>
+      </c>
+      <c r="AG13">
+        <v>45.2556341623514</v>
+      </c>
+      <c r="AH13">
         <v>11.849</v>
       </c>
+      <c r="AI13">
+        <v>43</v>
+      </c>
+      <c r="AJ13">
+        <v>-1.13998341560364</v>
+      </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:36">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
       <c r="B14">
+        <v>13.4500144412351</v>
+      </c>
+      <c r="C14">
+        <v>-0.579664349555969</v>
+      </c>
+      <c r="D14">
+        <v>-2.49788021735236</v>
+      </c>
+      <c r="F14">
+        <v>27.388449729504</v>
+      </c>
+      <c r="G14">
+        <v>16.3969666208873</v>
+      </c>
+      <c r="H14">
+        <v>14.6941589979995</v>
+      </c>
+      <c r="I14">
+        <v>40061753451.8</v>
+      </c>
+      <c r="J14">
         <v>2.22619979863525</v>
       </c>
-      <c r="C14">
+      <c r="K14">
+        <v>10342.4317112754</v>
+      </c>
+      <c r="L14">
+        <v>2996.0677072015</v>
+      </c>
+      <c r="M14">
+        <v>-0.0429670178954922</v>
+      </c>
+      <c r="N14">
+        <v>28.3</v>
+      </c>
+      <c r="O14">
+        <v>-0.681878209114075</v>
+      </c>
+      <c r="P14">
+        <v>11.1781214545889</v>
+      </c>
+      <c r="Q14">
+        <v>28.6894966262614</v>
+      </c>
+      <c r="R14">
+        <v>20.2282199796979</v>
+      </c>
+      <c r="S14">
+        <v>24.3148026512211</v>
+      </c>
+      <c r="T14">
         <v>7.11172943343081</v>
       </c>
-      <c r="D14">
+      <c r="U14">
         <v>19.4397903688734</v>
       </c>
-      <c r="E14">
+      <c r="V14">
+        <v>69.464</v>
+      </c>
+      <c r="W14">
+        <v>1.64817579267929</v>
+      </c>
+      <c r="X14">
+        <v>-10.0051949602914</v>
+      </c>
+      <c r="Y14">
+        <v>-1.43632972240448</v>
+      </c>
+      <c r="Z14">
+        <v>93161001</v>
+      </c>
+      <c r="AA14">
+        <v>1.2</v>
+      </c>
+      <c r="AB14">
+        <v>-0.385591775178909</v>
+      </c>
+      <c r="AC14">
+        <v>-0.536399841308594</v>
+      </c>
+      <c r="AD14">
         <v>12.3849047590613</v>
       </c>
-      <c r="F14">
+      <c r="AE14">
+        <v>15672467970.7728</v>
+      </c>
+      <c r="AF14">
+        <v>2.48779534146603</v>
+      </c>
+      <c r="AG14">
+        <v>40.7117692721084</v>
+      </c>
+      <c r="AH14">
         <v>12.597</v>
       </c>
+      <c r="AI14">
+        <v>42.946</v>
+      </c>
+      <c r="AJ14">
+        <v>-0.765063405036926</v>
+      </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:36">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
       <c r="B15">
+        <v>26.7924725126472</v>
+      </c>
+      <c r="C15">
+        <v>-0.614102065563202</v>
+      </c>
+      <c r="D15">
+        <v>-1.22513249838744</v>
+      </c>
+      <c r="F15">
+        <v>26.2224394958043</v>
+      </c>
+      <c r="G15">
+        <v>17.0178456245969</v>
+      </c>
+      <c r="H15">
+        <v>16.5588608179564</v>
+      </c>
+      <c r="I15">
+        <v>46534987114.9</v>
+      </c>
+      <c r="J15">
         <v>2.18546605362143</v>
       </c>
-      <c r="C15">
+      <c r="K15">
+        <v>10511.3931678495</v>
+      </c>
+      <c r="L15">
+        <v>3025.52563552448</v>
+      </c>
+      <c r="M15">
+        <v>-0.14323388107762</v>
+      </c>
+      <c r="O15">
+        <v>-0.782936871051788</v>
+      </c>
+      <c r="P15">
+        <v>11.3523973339067</v>
+      </c>
+      <c r="Q15">
+        <v>32.2017308105784</v>
+      </c>
+      <c r="R15">
+        <v>21.4163083207912</v>
+      </c>
+      <c r="S15">
+        <v>23.3551924317351</v>
+      </c>
+      <c r="T15">
         <v>9.46971981064917</v>
       </c>
-      <c r="D15">
+      <c r="U15">
         <v>22.5897666592664</v>
       </c>
-      <c r="E15">
+      <c r="V15">
+        <v>69.63200000000001</v>
+      </c>
+      <c r="W15">
+        <v>1.61005697699419</v>
+      </c>
+      <c r="X15">
+        <v>-12.6356159965599</v>
+      </c>
+      <c r="Y15">
+        <v>-1.63883090019226</v>
+      </c>
+      <c r="Z15">
+        <v>95333553</v>
+      </c>
+      <c r="AB15">
+        <v>-0.557433128356934</v>
+      </c>
+      <c r="AC15">
+        <v>-0.73585569858551</v>
+      </c>
+      <c r="AD15">
         <v>13.4980649322726</v>
       </c>
-      <c r="F15">
+      <c r="AE15">
+        <v>16536236826.4074</v>
+      </c>
+      <c r="AF15">
+        <v>2.73003963526374</v>
+      </c>
+      <c r="AG15">
+        <v>40.373038056332</v>
+      </c>
+      <c r="AH15">
         <v>13.154</v>
       </c>
+      <c r="AI15">
+        <v>42.893</v>
+      </c>
+      <c r="AJ15">
+        <v>-1.05164992809296</v>
+      </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:36">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
       <c r="B16">
+        <v>29.2880714168568</v>
+      </c>
+      <c r="C16">
+        <v>-0.575518012046814</v>
+      </c>
+      <c r="D16">
+        <v>-1.94849131455399</v>
+      </c>
+      <c r="F16">
+        <v>25.6066805392918</v>
+      </c>
+      <c r="G16">
+        <v>14.2441314553991</v>
+      </c>
+      <c r="H16">
+        <v>14.0020767838652</v>
+      </c>
+      <c r="I16">
+        <v>41772774970.9</v>
+      </c>
+      <c r="J16">
         <v>2.91591187985748</v>
       </c>
-      <c r="C16">
+      <c r="K16">
+        <v>10256.4367553616</v>
+      </c>
+      <c r="L16">
+        <v>3133.39102265541</v>
+      </c>
+      <c r="M16">
+        <v>0.599558564006458</v>
+      </c>
+      <c r="O16">
+        <v>-0.7166567444801329</v>
+      </c>
+      <c r="P16">
+        <v>11.849765258216</v>
+      </c>
+      <c r="Q16">
+        <v>32.9206291079812</v>
+      </c>
+      <c r="R16">
+        <v>19.8767136150235</v>
+      </c>
+      <c r="S16">
+        <v>22.6760563380282</v>
+      </c>
+      <c r="T16">
         <v>10.0702154687481</v>
       </c>
-      <c r="D16">
+      <c r="U16">
         <v>22.7221711517273</v>
       </c>
-      <c r="E16">
+      <c r="V16">
+        <v>69.911</v>
+      </c>
+      <c r="W16">
+        <v>1.68969483568075</v>
+      </c>
+      <c r="X16">
+        <v>-11.0277183098592</v>
+      </c>
+      <c r="Y16">
+        <v>-1.63117659091949</v>
+      </c>
+      <c r="Z16">
+        <v>97528654</v>
+      </c>
+      <c r="AB16">
+        <v>-0.687225043773651</v>
+      </c>
+      <c r="AC16">
+        <v>-0.698402404785156</v>
+      </c>
+      <c r="AD16">
         <v>12.2201408450704</v>
       </c>
-      <c r="F16">
+      <c r="AE16">
+        <v>14926998051.7397</v>
+      </c>
+      <c r="AF16">
+        <v>2.21204888604566</v>
+      </c>
+      <c r="AG16">
+        <v>36.9201877934272</v>
+      </c>
+      <c r="AH16">
         <v>13.105</v>
       </c>
+      <c r="AI16">
+        <v>42.839</v>
+      </c>
+      <c r="AJ16">
+        <v>-1.18009531497955</v>
+      </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:36">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
       <c r="B17">
+        <v>37.9385198263635</v>
+      </c>
+      <c r="C17">
+        <v>-0.600906729698181</v>
+      </c>
+      <c r="D17">
+        <v>-5.23529137853431</v>
+      </c>
+      <c r="F17">
+        <v>26.316393760305</v>
+      </c>
+      <c r="G17">
+        <v>13.1838454928598</v>
+      </c>
+      <c r="H17">
+        <v>15.4090910799379</v>
+      </c>
+      <c r="I17">
+        <v>49873938935.6</v>
+      </c>
+      <c r="J17">
         <v>4.37201907790141</v>
       </c>
-      <c r="C17">
+      <c r="K17">
+        <v>10903.3368231185</v>
+      </c>
+      <c r="L17">
+        <v>3306.98159414141</v>
+      </c>
+      <c r="M17">
+        <v>2.20415858015615</v>
+      </c>
+      <c r="N17">
+        <v>31.8</v>
+      </c>
+      <c r="O17">
+        <v>-0.690327763557434</v>
+      </c>
+      <c r="P17">
+        <v>11.7598919759401</v>
+      </c>
+      <c r="Q17">
+        <v>30.2303694913867</v>
+      </c>
+      <c r="R17">
+        <v>20.9886247391464</v>
+      </c>
+      <c r="S17">
+        <v>21.6620974671631</v>
+      </c>
+      <c r="T17">
         <v>10.370490343517</v>
       </c>
-      <c r="D17">
+      <c r="U17">
         <v>24.2332160259881</v>
       </c>
-      <c r="E17">
+      <c r="V17">
+        <v>70.13500000000001</v>
+      </c>
+      <c r="W17">
+        <v>1.72314742829085</v>
+      </c>
+      <c r="X17">
+        <v>-10.7275665943778</v>
+      </c>
+      <c r="Y17">
+        <v>-1.49933218955994</v>
+      </c>
+      <c r="Z17">
+        <v>99597342</v>
+      </c>
+      <c r="AA17">
+        <v>1.2</v>
+      </c>
+      <c r="AB17">
+        <v>-0.7963630557060239</v>
+      </c>
+      <c r="AC17">
+        <v>-0.601831138134003</v>
+      </c>
+      <c r="AD17">
         <v>12.5192110970171</v>
       </c>
-      <c r="F17">
+      <c r="AE17">
+        <v>15858887325.7756</v>
+      </c>
+      <c r="AF17">
+        <v>2.59707505474829</v>
+      </c>
+      <c r="AG17">
+        <v>34.8459429600229</v>
+      </c>
+      <c r="AH17">
         <v>13.052</v>
       </c>
+      <c r="AI17">
+        <v>42.785</v>
+      </c>
+      <c r="AJ17">
+        <v>-1.19008219242096</v>
+      </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:36">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
       <c r="B18">
+        <v>40.4634435641175</v>
+      </c>
+      <c r="C18">
+        <v>-0.590893149375916</v>
+      </c>
+      <c r="D18">
+        <v>-6.16465951871263</v>
+      </c>
+      <c r="F18">
+        <v>34.1348626252639</v>
+      </c>
+      <c r="G18">
+        <v>10.3454639403558</v>
+      </c>
+      <c r="H18">
+        <v>21.0959884446522</v>
+      </c>
+      <c r="I18">
+        <v>69188517055.2</v>
+      </c>
+      <c r="J18">
         <v>4.34664345555447</v>
       </c>
-      <c r="C18">
+      <c r="K18">
+        <v>10665.6676499685</v>
+      </c>
+      <c r="L18">
+        <v>3270.6287768197</v>
+      </c>
+      <c r="M18">
+        <v>2.24497375649698</v>
+      </c>
+      <c r="O18">
+        <v>-0.536168873310089</v>
+      </c>
+      <c r="P18">
+        <v>11.4268841809995</v>
+      </c>
+      <c r="S18">
+        <v>19.9010851110947</v>
+      </c>
+      <c r="T18">
         <v>13.813606214829</v>
       </c>
-      <c r="F18">
+      <c r="V18">
+        <v>70.437</v>
+      </c>
+      <c r="W18">
+        <v>1.66660515243227</v>
+      </c>
+      <c r="Y18">
+        <v>-1.43972682952881</v>
+      </c>
+      <c r="Z18">
+        <v>101644589</v>
+      </c>
+      <c r="AB18">
+        <v>-0.892875909805298</v>
+      </c>
+      <c r="AC18">
+        <v>-0.477475792169571</v>
+      </c>
+      <c r="AE18">
+        <v>23642691705.9678</v>
+      </c>
+      <c r="AF18">
+        <v>3.88541069587349</v>
+      </c>
+      <c r="AG18">
+        <v>30.2465490514505</v>
+      </c>
+      <c r="AH18">
         <v>12.45</v>
       </c>
+      <c r="AI18">
+        <v>42.732</v>
+      </c>
+      <c r="AJ18">
+        <v>-1.20482385158539</v>
+      </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:36">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
       <c r="B19">
+        <v>50.1146859513116</v>
+      </c>
+      <c r="C19">
+        <v>-0.495982348918915</v>
+      </c>
+      <c r="D19">
+        <v>-3.19681566782461</v>
+      </c>
+      <c r="F19">
+        <v>27.0698246737254</v>
+      </c>
+      <c r="G19">
+        <v>15.0140868185672</v>
+      </c>
+      <c r="H19">
+        <v>34.6961018574758</v>
+      </c>
+      <c r="I19">
+        <v>84587108845.3</v>
+      </c>
+      <c r="J19">
         <v>4.18122099994778</v>
       </c>
-      <c r="C19">
+      <c r="K19">
+        <v>11124.7351098149</v>
+      </c>
+      <c r="L19">
+        <v>2395.10333299491</v>
+      </c>
+      <c r="M19">
+        <v>2.12015477172733</v>
+      </c>
+      <c r="N19">
+        <v>31.5</v>
+      </c>
+      <c r="O19">
+        <v>-0.530632019042969</v>
+      </c>
+      <c r="P19">
+        <v>9.57903662572827</v>
+      </c>
+      <c r="S19">
+        <v>27.8180475395935</v>
+      </c>
+      <c r="T19">
         <v>29.5066083940039</v>
       </c>
-      <c r="F19">
+      <c r="V19">
+        <v>70.709</v>
+      </c>
+      <c r="W19">
+        <v>1.42203170028818</v>
+      </c>
+      <c r="Y19">
+        <v>-1.42964589595795</v>
+      </c>
+      <c r="Z19">
+        <v>103696057</v>
+      </c>
+      <c r="AA19">
+        <v>3.1</v>
+      </c>
+      <c r="AB19">
+        <v>-0.813245594501495</v>
+      </c>
+      <c r="AC19">
+        <v>-0.448036134243011</v>
+      </c>
+      <c r="AE19">
+        <v>36400242555.8255</v>
+      </c>
+      <c r="AF19">
+        <v>5.72306111855628</v>
+      </c>
+      <c r="AG19">
+        <v>42.8321343581608</v>
+      </c>
+      <c r="AH19">
         <v>11.767</v>
       </c>
+      <c r="AI19">
+        <v>42.705</v>
+      </c>
+      <c r="AJ19">
+        <v>-1.25143277645111</v>
+      </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:36">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
       <c r="B20">
+        <v>52.0176269964054</v>
+      </c>
+      <c r="C20">
+        <v>-0.514722347259521</v>
+      </c>
+      <c r="D20">
+        <v>-2.93164483711978</v>
+      </c>
+      <c r="F20">
+        <v>24.2952790707642</v>
+      </c>
+      <c r="G20">
+        <v>17.984655608418</v>
+      </c>
+      <c r="H20">
+        <v>38.8036123837843</v>
+      </c>
+      <c r="I20">
+        <v>99457163486.3</v>
+      </c>
+      <c r="J20">
         <v>5.3311086189448</v>
       </c>
-      <c r="C20">
+      <c r="K20">
+        <v>12329.2446781436</v>
+      </c>
+      <c r="L20">
+        <v>2484.70315630508</v>
+      </c>
+      <c r="M20">
+        <v>3.35166753247044</v>
+      </c>
+      <c r="O20">
+        <v>-0.454036295413971</v>
+      </c>
+      <c r="P20">
+        <v>7.94222279370794</v>
+      </c>
+      <c r="S20">
+        <v>27.9263640649779</v>
+      </c>
+      <c r="T20">
         <v>14.4014657807422</v>
       </c>
-      <c r="F20">
+      <c r="V20">
+        <v>70.974</v>
+      </c>
+      <c r="W20">
+        <v>1.24996619642133</v>
+      </c>
+      <c r="Y20">
+        <v>-1.18812155723572</v>
+      </c>
+      <c r="Z20">
+        <v>105682094</v>
+      </c>
+      <c r="AB20">
+        <v>-0.804274797439575</v>
+      </c>
+      <c r="AC20">
+        <v>-0.301445573568344</v>
+      </c>
+      <c r="AE20">
+        <v>41839242990.7097</v>
+      </c>
+      <c r="AF20">
+        <v>5.85734270401284</v>
+      </c>
+      <c r="AG20">
+        <v>45.9110196733959</v>
+      </c>
+      <c r="AH20">
         <v>9.855</v>
       </c>
+      <c r="AI20">
+        <v>42.704</v>
+      </c>
+      <c r="AJ20">
+        <v>-1.32450354099274</v>
+      </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:36">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
       <c r="B21">
+        <v>49.4407828459412</v>
+      </c>
+      <c r="C21">
+        <v>-0.655317544937134</v>
+      </c>
+      <c r="D21">
+        <v>-3.20758543154938</v>
+      </c>
+      <c r="F21">
+        <v>22.8487308972763</v>
+      </c>
+      <c r="G21">
+        <v>16.6440314510365</v>
+      </c>
+      <c r="H21">
+        <v>37.3486377137165</v>
+      </c>
+      <c r="I21">
+        <v>114910260649.9</v>
+      </c>
+      <c r="J21">
         <v>5.55209307156956</v>
       </c>
-      <c r="C21">
+      <c r="K21">
+        <v>13363.732696323</v>
+      </c>
+      <c r="L21">
+        <v>2962.98892023003</v>
+      </c>
+      <c r="M21">
+        <v>3.71584088573542</v>
+      </c>
+      <c r="N21">
+        <v>31.9</v>
+      </c>
+      <c r="O21">
+        <v>-0.251354306936264</v>
+      </c>
+      <c r="P21">
+        <v>7.2855611150822</v>
+      </c>
+      <c r="S21">
+        <v>24.4799857040743</v>
+      </c>
+      <c r="T21">
         <v>9.152799593248041</v>
       </c>
-      <c r="F21">
+      <c r="V21">
+        <v>71.21299999999999</v>
+      </c>
+      <c r="W21">
+        <v>1.18097179684711</v>
+      </c>
+      <c r="Y21">
+        <v>-1.12463080883026</v>
+      </c>
+      <c r="Z21">
+        <v>107553158</v>
+      </c>
+      <c r="AA21">
+        <v>2</v>
+      </c>
+      <c r="AB21">
+        <v>-0.758563220500946</v>
+      </c>
+      <c r="AC21">
+        <v>-0.332123339176178</v>
+      </c>
+      <c r="AE21">
+        <v>44568837112.0669</v>
+      </c>
+      <c r="AF21">
+        <v>5.83923947440236</v>
+      </c>
+      <c r="AG21">
+        <v>41.1240171551108</v>
+      </c>
+      <c r="AH21">
         <v>7.851</v>
       </c>
+      <c r="AI21">
+        <v>42.73</v>
+      </c>
+      <c r="AJ21">
+        <v>-1.44394659996033</v>
+      </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:36">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
       <c r="B22">
+        <v>31.2403292398494</v>
+      </c>
+      <c r="C22">
+        <v>-0.810433626174927</v>
+      </c>
+      <c r="D22">
+        <v>-3.70903990583375</v>
+      </c>
+      <c r="F22">
+        <v>25.7894742547866</v>
+      </c>
+      <c r="G22">
+        <v>12.4727757370868</v>
+      </c>
+      <c r="H22">
+        <v>35.5843178235706</v>
+      </c>
+      <c r="I22">
+        <v>132538717154</v>
+      </c>
+      <c r="J22">
         <v>3.55016483786838</v>
       </c>
-      <c r="C22">
+      <c r="K22">
+        <v>15231.865417764</v>
+      </c>
+      <c r="L22">
+        <v>3511.11381026379</v>
+      </c>
+      <c r="M22">
+        <v>1.88111975917718</v>
+      </c>
+      <c r="O22">
+        <v>-0.44617161154747</v>
+      </c>
+      <c r="P22">
+        <v>7.5399018301206</v>
+      </c>
+      <c r="S22">
+        <v>19.6534798296655</v>
+      </c>
+      <c r="T22">
         <v>5.04493288977539</v>
       </c>
-      <c r="F22">
+      <c r="V22">
+        <v>69.79000000000001</v>
+      </c>
+      <c r="W22">
+        <v>1.12247550332399</v>
+      </c>
+      <c r="Y22">
+        <v>-1.18193280696869</v>
+      </c>
+      <c r="Z22">
+        <v>109315124</v>
+      </c>
+      <c r="AB22">
+        <v>-0.571031153202057</v>
+      </c>
+      <c r="AC22">
+        <v>-0.317483067512512</v>
+      </c>
+      <c r="AE22">
+        <v>38972812936.6708</v>
+      </c>
+      <c r="AF22">
+        <v>5.56473451430895</v>
+      </c>
+      <c r="AG22">
+        <v>32.1262555667523</v>
+      </c>
+      <c r="AH22">
         <v>7.974</v>
       </c>
+      <c r="AI22">
+        <v>42.783</v>
+      </c>
+      <c r="AJ22">
+        <v>-1.48189222812653</v>
+      </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:36">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
       <c r="B23">
+        <v>46.9269118720521</v>
+      </c>
+      <c r="C23">
+        <v>-0.70594334602356</v>
+      </c>
+      <c r="D23">
+        <v>-4.38240299812001</v>
+      </c>
+      <c r="F23">
+        <v>28.2307543894277</v>
+      </c>
+      <c r="G23">
+        <v>10.5611502153652</v>
+      </c>
+      <c r="H23">
+        <v>35.4130599251787</v>
+      </c>
+      <c r="I23">
+        <v>145998330659.9</v>
+      </c>
+      <c r="J23">
         <v>3.29064601202211</v>
       </c>
-      <c r="C23">
+      <c r="K23">
+        <v>15579.0160861551</v>
+      </c>
+      <c r="L23">
+        <v>3827.35415374308</v>
+      </c>
+      <c r="M23">
+        <v>1.76220484283698</v>
+      </c>
+      <c r="N23">
+        <v>28.5</v>
+      </c>
+      <c r="O23">
+        <v>-0.457696795463562</v>
+      </c>
+      <c r="P23">
+        <v>7.55804355330102</v>
+      </c>
+      <c r="S23">
+        <v>19.295823265447</v>
+      </c>
+      <c r="T23">
         <v>5.21404940513041</v>
       </c>
-      <c r="F23">
+      <c r="V23">
+        <v>68.976</v>
+      </c>
+      <c r="W23">
+        <v>1.12200927143154</v>
+      </c>
+      <c r="Y23">
+        <v>-1.0328643321991</v>
+      </c>
+      <c r="Z23">
+        <v>110957008</v>
+      </c>
+      <c r="AA23">
+        <v>1.4</v>
+      </c>
+      <c r="AB23">
+        <v>-0.519896507263184</v>
+      </c>
+      <c r="AC23">
+        <v>-0.260645717382431</v>
+      </c>
+      <c r="AE23">
+        <v>39824388217.3615</v>
+      </c>
+      <c r="AF23">
+        <v>4.38225643427728</v>
+      </c>
+      <c r="AG23">
+        <v>29.8569734808122</v>
+      </c>
+      <c r="AH23">
         <v>7.441</v>
       </c>
+      <c r="AI23">
+        <v>42.862</v>
+      </c>
+      <c r="AJ23">
+        <v>-1.50513410568237</v>
+      </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:36">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
       <c r="B24">
+        <v>39.247162300731</v>
+      </c>
+      <c r="C24">
+        <v>-0.678962171077728</v>
+      </c>
+      <c r="D24">
+        <v>-2.2100904275198</v>
+      </c>
+      <c r="F24">
+        <v>30.847002116672</v>
+      </c>
+      <c r="G24">
+        <v>15.0870258208479</v>
+      </c>
+      <c r="H24">
+        <v>35.3791611645131</v>
+      </c>
+      <c r="I24">
+        <v>163092456403.3</v>
+      </c>
+      <c r="J24">
         <v>6.58784560886967</v>
       </c>
-      <c r="C24">
+      <c r="K24">
+        <v>17526.8017030166</v>
+      </c>
+      <c r="L24">
+        <v>4233.30783744856</v>
+      </c>
+      <c r="M24">
+        <v>5.01555864991792</v>
+      </c>
+      <c r="O24">
+        <v>-0.448231309652328</v>
+      </c>
+      <c r="P24">
+        <v>7.26809053235575</v>
+      </c>
+      <c r="S24">
+        <v>21.8960790564233</v>
+      </c>
+      <c r="T24">
         <v>13.8956609775178</v>
       </c>
-      <c r="F24">
+      <c r="V24">
+        <v>71.01000000000001</v>
+      </c>
+      <c r="W24">
+        <v>1.04848151432161</v>
+      </c>
+      <c r="Y24">
+        <v>-0.978700578212738</v>
+      </c>
+      <c r="Z24">
+        <v>112618250</v>
+      </c>
+      <c r="AB24">
+        <v>-0.713920831680298</v>
+      </c>
+      <c r="AC24">
+        <v>-0.26560452580452</v>
+      </c>
+      <c r="AE24">
+        <v>32143926008.4607</v>
+      </c>
+      <c r="AF24">
+        <v>3.32738146369502</v>
+      </c>
+      <c r="AG24">
+        <v>36.9831048772713</v>
+      </c>
+      <c r="AH24">
         <v>7.344</v>
       </c>
+      <c r="AI24">
+        <v>42.967</v>
+      </c>
+      <c r="AJ24">
+        <v>-1.45044994354248</v>
+      </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:36">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
       <c r="B25">
+        <v>38.632414751384</v>
+      </c>
+      <c r="C25">
+        <v>-0.7477903962135311</v>
+      </c>
+      <c r="D25">
+        <v>-3.17338760075616</v>
+      </c>
+      <c r="F25">
+        <v>29.2578215393463</v>
+      </c>
+      <c r="G25">
+        <v>19.1060913405676</v>
+      </c>
+      <c r="H25">
+        <v>44.3806069059616</v>
+      </c>
+      <c r="I25">
+        <v>168062300503.6</v>
+      </c>
+      <c r="J25">
         <v>3.76028052279247</v>
       </c>
-      <c r="C25">
+      <c r="K25">
+        <v>18524.8392997937</v>
+      </c>
+      <c r="L25">
+        <v>3456.78968456253</v>
+      </c>
+      <c r="M25">
+        <v>2.02315842412948</v>
+      </c>
+      <c r="O25">
+        <v>-0.239516973495483</v>
+      </c>
+      <c r="P25">
+        <v>6.78850660732221</v>
+      </c>
+      <c r="S25">
+        <v>21.3443094314355</v>
+      </c>
+      <c r="T25">
         <v>33.8847763115546</v>
       </c>
-      <c r="F25">
+      <c r="V25">
+        <v>71.633</v>
+      </c>
+      <c r="W25">
+        <v>0.870565509711049</v>
+      </c>
+      <c r="Y25">
+        <v>-0.8667643070220949</v>
+      </c>
+      <c r="Z25">
+        <v>114535772</v>
+      </c>
+      <c r="AB25">
+        <v>-0.665456295013428</v>
+      </c>
+      <c r="AC25">
+        <v>-0.184178426861763</v>
+      </c>
+      <c r="AE25">
+        <v>33070180836.1374</v>
+      </c>
+      <c r="AF25">
+        <v>3.87390992001782</v>
+      </c>
+      <c r="AG25">
+        <v>40.4504007720031</v>
+      </c>
+      <c r="AH25">
         <v>7.334</v>
       </c>
+      <c r="AI25">
+        <v>43.1</v>
+      </c>
+      <c r="AJ25">
+        <v>-1.37938976287842</v>
+      </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:36">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
       <c r="B26">
+        <v>30.1330844537785</v>
+      </c>
+      <c r="D26">
+        <v>-5.72048144014406</v>
+      </c>
+      <c r="F26">
+        <v>27.5692279729149</v>
+      </c>
+      <c r="G26">
+        <v>16.3762422101126</v>
+      </c>
+      <c r="J26">
         <v>2.3991692678251</v>
       </c>
-      <c r="C26">
+      <c r="K26">
+        <v>19094.1449444111</v>
+      </c>
+      <c r="L26">
+        <v>3338.47371395895</v>
+      </c>
+      <c r="M26">
+        <v>0.639636335125445</v>
+      </c>
+      <c r="P26">
+        <v>6.27031988169153</v>
+      </c>
+      <c r="S26">
+        <v>23.2245098772607</v>
+      </c>
+      <c r="T26">
         <v>28.2705899322083</v>
       </c>
-      <c r="F26">
+      <c r="Z26">
+        <v>116538258</v>
+      </c>
+      <c r="AE26">
+        <v>44921341018.4659</v>
+      </c>
+      <c r="AF26">
+        <v>4.53950764706678</v>
+      </c>
+      <c r="AG26">
+        <v>39.6007520873733</v>
+      </c>
+      <c r="AH26">
         <v>7.198</v>
+      </c>
+      <c r="AI26">
+        <v>43.258</v>
       </c>
     </row>
   </sheetData>

--- a/EGY_WB_timeseries.xlsx
+++ b/EGY_WB_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Control of Corruption</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t>Foreign direct investment, net outflows (BoP, current US$)</t>
+  </si>
+  <si>
+    <t>GDP (current US$)</t>
   </si>
   <si>
     <t>GDP growth (annual %)</t>
@@ -446,12 +449,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y36"/>
+  <dimension ref="A1:Z36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -525,8 +528,11 @@
       <c r="Y1" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:25">
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26">
       <c r="A2" s="1">
         <v>1990</v>
       </c>
@@ -549,46 +555,49 @@
         <v>12000000</v>
       </c>
       <c r="J2">
+        <v>42978914311.3504</v>
+      </c>
+      <c r="K2">
         <v>5.66702915715818</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>735.9829350280251</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>32</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>11.3778705636743</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>24.1137787056367</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>23.0469728601253</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>32.5678496868476</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>16.2763516730877</v>
       </c>
-      <c r="S2">
+      <c r="T2">
         <v>-1.95720250521921</v>
       </c>
-      <c r="U2">
+      <c r="V2">
         <v>13.2348643006263</v>
       </c>
-      <c r="V2">
+      <c r="W2">
         <v>3619931742.61285</v>
       </c>
-      <c r="W2">
+      <c r="X2">
         <v>2.7202192317211</v>
       </c>
-      <c r="X2">
+      <c r="Y2">
         <v>52.9227557411273</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:26">
       <c r="A3" s="1">
         <v>1991</v>
       </c>
@@ -611,46 +620,49 @@
         <v>62000000</v>
       </c>
       <c r="J3">
+        <v>37387836490.5284</v>
+      </c>
+      <c r="K3">
         <v>1.12540459520747</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>622.829605007867</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>11.1111111111111</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>27.3128888888889</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>29.3928888888889</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>35.3777777777778</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>19.1362645230579</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>2.44533333333333</v>
       </c>
-      <c r="U3">
+      <c r="V3">
         <v>14.7377777777778</v>
       </c>
-      <c r="V3">
+      <c r="W3">
         <v>6185285500.81964</v>
       </c>
-      <c r="W3">
+      <c r="X3">
         <v>4.8391854224694</v>
       </c>
-      <c r="X3">
+      <c r="Y3">
         <v>62.8444444444444</v>
       </c>
-      <c r="Y3">
+      <c r="Z3">
         <v>9.380000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:26">
       <c r="A4" s="1">
         <v>1992</v>
       </c>
@@ -673,46 +685,49 @@
         <v>4000000</v>
       </c>
       <c r="J4">
+        <v>41855986519.4235</v>
+      </c>
+      <c r="K4">
         <v>4.47285918408184</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>680.7992386455099</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>10.4241552839684</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>34.9439252336449</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>32.6513299784328</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>30.9130122214234</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>18.079700454667</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>-1.17469446441409</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>18.4802300503235</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <v>11620220747.8378</v>
       </c>
-      <c r="W4">
+      <c r="X4">
         <v>8.417908178331031</v>
       </c>
-      <c r="X4">
+      <c r="Y4">
         <v>59.3098490294752</v>
       </c>
-      <c r="Y4">
+      <c r="Z4">
         <v>8.92</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:26">
       <c r="A5" s="1">
         <v>1993</v>
       </c>
@@ -735,46 +750,49 @@
         <v>25000000</v>
       </c>
       <c r="J5">
+        <v>46578631452.581</v>
+      </c>
+      <c r="K5">
         <v>2.90079079959442</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>740.334217356418</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>10.3092783505155</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>31.4845360824742</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>34.8311855670103</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>30.090206185567</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>27.4905861165684</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>4.23260309278351</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>18.764175257732</v>
       </c>
-      <c r="V5">
+      <c r="W5">
         <v>13854276438.8218</v>
       </c>
-      <c r="W5">
+      <c r="X5">
         <v>9.633848135009661</v>
       </c>
-      <c r="X5">
+      <c r="Y5">
         <v>55.9278350515464</v>
       </c>
-      <c r="Y5">
+      <c r="Z5">
         <v>10.92</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:26">
       <c r="A6" s="1">
         <v>1994</v>
       </c>
@@ -797,46 +815,49 @@
         <v>43000000</v>
       </c>
       <c r="J6">
+        <v>51897983392.6453</v>
+      </c>
+      <c r="K6">
         <v>3.97317218034541</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>807.303537230487</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>10.2857142857143</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>31</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>36.9085714285714</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>28.0571428571429</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <v>30.6930875576037</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <v>3.004</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>19.0474285714286</v>
       </c>
-      <c r="V6">
+      <c r="W6">
         <v>14412967684.9265</v>
       </c>
-      <c r="W6">
+      <c r="X6">
         <v>9.74068552709609</v>
       </c>
-      <c r="X6">
+      <c r="Y6">
         <v>50.6285714285714</v>
       </c>
-      <c r="Y6">
+      <c r="Z6">
         <v>10.93</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:26">
       <c r="A7" s="1">
         <v>1995</v>
       </c>
@@ -859,49 +880,52 @@
         <v>93000000</v>
       </c>
       <c r="J7">
+        <v>60159245060.4541</v>
+      </c>
+      <c r="K7">
         <v>4.64245877240639</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>916.326617700876</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>30.1</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>10.5392156862745</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>28.125</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>34.7676470588235</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>27.6960784313726</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <v>26.0217864923747</v>
       </c>
-      <c r="S7">
+      <c r="T7">
         <v>3.44166666666667</v>
       </c>
-      <c r="U7">
+      <c r="V7">
         <v>17.6230392156863</v>
       </c>
-      <c r="V7">
+      <c r="W7">
         <v>17121798673.9485</v>
       </c>
-      <c r="W7">
+      <c r="X7">
         <v>10.7442129418701</v>
       </c>
-      <c r="X7">
+      <c r="Y7">
         <v>50.2450980392157</v>
       </c>
-      <c r="Y7">
+      <c r="Z7">
         <v>11.04</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:26">
       <c r="A8" s="1">
         <v>1996</v>
       </c>
@@ -927,49 +951,52 @@
         <v>5000000</v>
       </c>
       <c r="J8">
+        <v>67629716981.1321</v>
+      </c>
+      <c r="K8">
         <v>4.98873056512208</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>1008.97637629447</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>10.3748910200523</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>26.9481255448997</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>28.6625980819529</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>26.1987794245859</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>25.933774405927</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <v>-1.40061028770706</v>
       </c>
-      <c r="T8">
+      <c r="U8">
         <v>-0.526031970977783</v>
       </c>
-      <c r="U8">
+      <c r="V8">
         <v>17.4629468177855</v>
       </c>
-      <c r="V8">
+      <c r="W8">
         <v>18296476060.6246</v>
       </c>
-      <c r="W8">
+      <c r="X8">
         <v>11.0837353085716</v>
       </c>
-      <c r="X8">
+      <c r="Y8">
         <v>46.9485614646905</v>
       </c>
-      <c r="Y8">
+      <c r="Z8">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:26">
       <c r="A9" s="1">
         <v>1997</v>
       </c>
@@ -992,46 +1019,49 @@
         <v>129200000</v>
       </c>
       <c r="J9">
+        <v>78436578171.0914</v>
+      </c>
+      <c r="K9">
         <v>5.49235474302942</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>1146.20172117634</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>11.320045129748</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>24.2320421210982</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>26.0060172997367</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>24.8965776607747</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>23.986156162215</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <v>-1.62805566002256</v>
       </c>
-      <c r="U9">
+      <c r="V9">
         <v>15.9646483640466</v>
       </c>
-      <c r="V9">
+      <c r="W9">
         <v>19370588197.9808</v>
       </c>
-      <c r="W9">
+      <c r="X9">
         <v>10.5123535115083</v>
       </c>
-      <c r="X9">
+      <c r="Y9">
         <v>43.7382474614517</v>
       </c>
-      <c r="Y9">
+      <c r="Z9">
         <v>8.369999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:26">
       <c r="A10" s="1">
         <v>1998</v>
       </c>
@@ -1057,34 +1087,37 @@
         <v>45000000</v>
       </c>
       <c r="J10">
+        <v>84828807556.08031</v>
+      </c>
+      <c r="K10">
         <v>5.575497460986</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>1212.82259820477</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>11.3082811412665</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>25.7132915796799</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <v>-0.0207697190344334</v>
       </c>
-      <c r="V10">
+      <c r="W10">
         <v>18823907998.2299</v>
       </c>
-      <c r="W10">
+      <c r="X10">
         <v>10.1824240884763</v>
       </c>
-      <c r="X10">
+      <c r="Y10">
         <v>41.9276270006959</v>
       </c>
-      <c r="Y10">
+      <c r="Z10">
         <v>8.029999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:26">
       <c r="A11" s="1">
         <v>1999</v>
       </c>
@@ -1107,34 +1140,37 @@
         <v>37500000</v>
       </c>
       <c r="J11">
+        <v>90710704806.8416</v>
+      </c>
+      <c r="K11">
         <v>6.05343878467555</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>1268.30949160496</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>30.8</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>11.6059817945384</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>23.3094928478544</v>
       </c>
-      <c r="V11">
+      <c r="W11">
         <v>15190021676.7155</v>
       </c>
-      <c r="W11">
+      <c r="X11">
         <v>8.04371613685888</v>
       </c>
-      <c r="X11">
+      <c r="Y11">
         <v>38.3615084525358</v>
       </c>
-      <c r="Y11">
+      <c r="Z11">
         <v>7.95</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:26">
       <c r="A12" s="1">
         <v>2000</v>
       </c>
@@ -1160,34 +1196,37 @@
         <v>51000000</v>
       </c>
       <c r="J12">
+        <v>99838543960.07629</v>
+      </c>
+      <c r="K12">
         <v>6.37000382991766</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>1366.09274372613</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>11.2025874742723</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>22.8168185827698</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <v>0.0497975237667561</v>
       </c>
-      <c r="V12">
+      <c r="W12">
         <v>13785040867.624</v>
       </c>
-      <c r="W12">
+      <c r="X12">
         <v>6.92773642731755</v>
       </c>
-      <c r="X12">
+      <c r="Y12">
         <v>39.0179359012055</v>
       </c>
-      <c r="Y12">
+      <c r="Z12">
         <v>8.98</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:26">
       <c r="A13" s="1">
         <v>2001</v>
       </c>
@@ -1210,31 +1249,34 @@
         <v>12400000</v>
       </c>
       <c r="J13">
+        <v>96684636118.5984</v>
+      </c>
+      <c r="K13">
         <v>3.53525197391507</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>1295.1374184163</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>11.318650683022</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>22.330638416504</v>
       </c>
-      <c r="V13">
+      <c r="W13">
         <v>13598234040.4969</v>
       </c>
-      <c r="W13">
+      <c r="X13">
         <v>7.45748900818796</v>
       </c>
-      <c r="X13">
+      <c r="Y13">
         <v>39.8104265402844</v>
       </c>
-      <c r="Y13">
+      <c r="Z13">
         <v>9.26</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:26">
       <c r="A14" s="1">
         <v>2002</v>
       </c>
@@ -1260,49 +1302,52 @@
         <v>27800000</v>
       </c>
       <c r="J14">
+        <v>85146067415.7303</v>
+      </c>
+      <c r="K14">
         <v>2.39020402573726</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>1116.82884626213</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>12.5890736342043</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>27.2483504882555</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>24.349696489839</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>22.6708894167326</v>
       </c>
-      <c r="R14">
+      <c r="S14">
         <v>19.665065282244</v>
       </c>
-      <c r="S14">
+      <c r="T14">
         <v>-6.74531538664555</v>
       </c>
-      <c r="T14">
+      <c r="U14">
         <v>-0.414172112941742</v>
       </c>
-      <c r="U14">
+      <c r="V14">
         <v>13.4077593032462</v>
       </c>
-      <c r="V14">
+      <c r="W14">
         <v>14076054422.998</v>
       </c>
-      <c r="W14">
+      <c r="X14">
         <v>8.250266346708729</v>
       </c>
-      <c r="X14">
+      <c r="Y14">
         <v>40.9870678279229</v>
       </c>
-      <c r="Y14">
+      <c r="Z14">
         <v>10.01</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:26">
       <c r="A15" s="1">
         <v>2003</v>
       </c>
@@ -1328,49 +1373,52 @@
         <v>20700000</v>
       </c>
       <c r="J15">
+        <v>80288461538.4615</v>
+      </c>
+      <c r="K15">
         <v>3.19345473739745</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>1031.27556291284</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>12.6706586826347</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>27.3324550898204</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>25.4311377245509</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>24.3832335329341</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <v>20.7925477377687</v>
       </c>
-      <c r="S15">
+      <c r="T15">
         <v>-5.8162874251497</v>
       </c>
-      <c r="T15">
+      <c r="U15">
         <v>-0.640924513339996</v>
       </c>
-      <c r="U15">
+      <c r="V15">
         <v>13.3499401197605</v>
       </c>
-      <c r="V15">
+      <c r="W15">
         <v>14603576021.3741</v>
       </c>
-      <c r="W15">
+      <c r="X15">
         <v>8.55089573372287</v>
       </c>
-      <c r="X15">
+      <c r="Y15">
         <v>46.1796407185629</v>
       </c>
-      <c r="Y15">
+      <c r="Z15">
         <v>10.91</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:26">
       <c r="A16" s="1">
         <v>2004</v>
       </c>
@@ -1396,52 +1444,55 @@
         <v>158900000</v>
       </c>
       <c r="J16">
+        <v>78782467532.4675</v>
+      </c>
+      <c r="K16">
         <v>4.0920716112534</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>991.255689145253</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>31.8</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>12.7549969091284</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>26.8903770863383</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>24.6404286008654</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>29.5899443643107</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <v>21.0859853332209</v>
       </c>
-      <c r="S16">
+      <c r="T16">
         <v>-5.61055017514939</v>
       </c>
-      <c r="T16">
+      <c r="U16">
         <v>-0.822401702404022</v>
       </c>
-      <c r="U16">
+      <c r="V16">
         <v>13.8359777457243</v>
       </c>
-      <c r="V16">
+      <c r="W16">
         <v>15338514716.8958</v>
       </c>
-      <c r="W16">
+      <c r="X16">
         <v>6.63684137548043</v>
       </c>
-      <c r="X16">
+      <c r="Y16">
         <v>57.8199052132701</v>
       </c>
-      <c r="Y16">
+      <c r="Z16">
         <v>10.32</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:26">
       <c r="A17" s="1">
         <v>2005</v>
       </c>
@@ -1467,49 +1518,52 @@
         <v>92000000</v>
       </c>
       <c r="J17">
+        <v>89660339660.33971</v>
+      </c>
+      <c r="K17">
         <v>4.47174447174434</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>1105.53920713903</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>12.7390900649954</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>27.3888579387187</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>24.2916620241411</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>32.6090993500464</v>
       </c>
-      <c r="R17">
+      <c r="S17">
         <v>20.2089647363532</v>
       </c>
-      <c r="S17">
+      <c r="T17">
         <v>-6.44885793871866</v>
       </c>
-      <c r="T17">
+      <c r="U17">
         <v>-0.629358649253845</v>
       </c>
-      <c r="U17">
+      <c r="V17">
         <v>14.068635097493</v>
       </c>
-      <c r="V17">
+      <c r="W17">
         <v>21856784928.5556</v>
       </c>
-      <c r="W17">
+      <c r="X17">
         <v>7.32906037591457</v>
       </c>
-      <c r="X17">
+      <c r="Y17">
         <v>62.9526462395543</v>
       </c>
-      <c r="Y17">
+      <c r="Z17">
         <v>11.049</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:26">
       <c r="A18" s="1">
         <v>2006</v>
       </c>
@@ -1535,49 +1589,52 @@
         <v>148400000</v>
       </c>
       <c r="J18">
+        <v>107426086956.522</v>
+      </c>
+      <c r="K18">
         <v>6.84383819379117</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>1298.97900203124</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>12.2875182127246</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>32.7636716852841</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>28.1389833252388</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>31.5687226809131</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <v>17.2010542481219</v>
       </c>
-      <c r="S18">
+      <c r="T18">
         <v>-7.1684960336733</v>
       </c>
-      <c r="T18">
+      <c r="U18">
         <v>-0.837807655334473</v>
       </c>
-      <c r="U18">
+      <c r="V18">
         <v>15.8295127084345</v>
       </c>
-      <c r="V18">
+      <c r="W18">
         <v>26006845068.1543</v>
       </c>
-      <c r="W18">
+      <c r="X18">
         <v>7.36480504492886</v>
       </c>
-      <c r="X18">
+      <c r="Y18">
         <v>61.5185365063947</v>
       </c>
-      <c r="Y18">
+      <c r="Z18">
         <v>10.49</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:26">
       <c r="A19" s="1">
         <v>2007</v>
       </c>
@@ -1606,49 +1663,52 @@
         <v>664800000</v>
       </c>
       <c r="J19">
+        <v>130437828371.278</v>
+      </c>
+      <c r="K19">
         <v>7.08782742681038</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>1547.74170735909</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>11.3319011815252</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>29.3352309344791</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>27.1170918367347</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>34.828141783029</v>
       </c>
-      <c r="R19">
+      <c r="S19">
         <v>17.560305150653</v>
       </c>
-      <c r="S19">
+      <c r="T19">
         <v>-4.55796186895811</v>
       </c>
-      <c r="T19">
+      <c r="U19">
         <v>-0.552382111549377</v>
       </c>
-      <c r="U19">
+      <c r="V19">
         <v>15.3498523093448</v>
       </c>
-      <c r="V19">
+      <c r="W19">
         <v>32214421786.3476</v>
       </c>
-      <c r="W19">
+      <c r="X19">
         <v>6.95056522562452</v>
       </c>
-      <c r="X19">
+      <c r="Y19">
         <v>65.07787325456501</v>
       </c>
-      <c r="Y19">
+      <c r="Z19">
         <v>8.800000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:26">
       <c r="A20" s="1">
         <v>2008</v>
       </c>
@@ -1674,52 +1734,55 @@
         <v>1920200000</v>
       </c>
       <c r="J20">
+        <v>162818181818.182</v>
+      </c>
+      <c r="K20">
         <v>7.15628356605819</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>1896.21594269779</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>31.1</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>10.8877721943049</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>30.3182043551089</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>27.6239352317141</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>38.6376326074819</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <v>15.0853305376009</v>
       </c>
-      <c r="S20">
+      <c r="T20">
         <v>-6.36079061976549</v>
       </c>
-      <c r="T20">
+      <c r="U20">
         <v>-0.510431706905365</v>
       </c>
-      <c r="U20">
+      <c r="V20">
         <v>15.3205248464545</v>
       </c>
-      <c r="V20">
+      <c r="W20">
         <v>34330505048.3926</v>
       </c>
-      <c r="W20">
+      <c r="X20">
         <v>5.97060049450951</v>
       </c>
-      <c r="X20">
+      <c r="Y20">
         <v>71.6806253489671</v>
       </c>
-      <c r="Y20">
+      <c r="Z20">
         <v>8.516999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:26">
       <c r="A21" s="1">
         <v>2009</v>
       </c>
@@ -1745,49 +1808,52 @@
         <v>571200000</v>
       </c>
       <c r="J21">
+        <v>189147005444.646</v>
+      </c>
+      <c r="K21">
         <v>4.67359979952391</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>2161.63964573927</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>11.3509882939935</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>30.0771253118403</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>26.9200729226636</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>31.596622529265</v>
       </c>
-      <c r="R21">
+      <c r="S21">
         <v>13.958581501277</v>
       </c>
-      <c r="S21">
+      <c r="T21">
         <v>-6.56296296296296</v>
       </c>
-      <c r="T21">
+      <c r="U21">
         <v>-0.607227087020874</v>
       </c>
-      <c r="U21">
+      <c r="V21">
         <v>15.6613605833813</v>
       </c>
-      <c r="V21">
+      <c r="W21">
         <v>34896678266.342</v>
       </c>
-      <c r="W21">
+      <c r="X21">
         <v>7.35827452765158</v>
       </c>
-      <c r="X21">
+      <c r="Y21">
         <v>56.5534446363462</v>
       </c>
-      <c r="Y21">
+      <c r="Z21">
         <v>9.087</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:26">
       <c r="A22" s="1">
         <v>2010</v>
       </c>
@@ -1813,52 +1879,55 @@
         <v>1175500000</v>
       </c>
       <c r="J22">
+        <v>218983666061.706</v>
+      </c>
+      <c r="K22">
         <v>5.1472348575531</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>2455.08194645282</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>30.2</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>11.163600198906</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>28.8602519476214</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>24.7838223106249</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>26.5871042599039</v>
       </c>
-      <c r="R22">
+      <c r="S22">
         <v>17.8615837104332</v>
       </c>
-      <c r="S22">
+      <c r="T22">
         <v>-7.73391347588264</v>
       </c>
-      <c r="T22">
+      <c r="U22">
         <v>-0.898418307304382</v>
       </c>
-      <c r="U22">
+      <c r="V22">
         <v>14.1300762473065</v>
       </c>
-      <c r="V22">
+      <c r="W22">
         <v>37028506134.5559</v>
       </c>
-      <c r="W22">
+      <c r="X22">
         <v>6.70121378987163</v>
       </c>
-      <c r="X22">
+      <c r="Y22">
         <v>47.9363500745898</v>
       </c>
-      <c r="Y22">
+      <c r="Z22">
         <v>8.757</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:26">
       <c r="A23" s="1">
         <v>2011</v>
       </c>
@@ -1884,52 +1953,55 @@
         <v>625500000</v>
       </c>
       <c r="J23">
+        <v>235989672977.625</v>
+      </c>
+      <c r="K23">
         <v>1.7645719489982</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>2590.64384891965</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>11.4506600539713</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>29.1899277952009</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>21.9307417402086</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>24.6882065494858</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>10.0649259874818</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <v>19.0798082369558</v>
       </c>
-      <c r="S23">
+      <c r="T23">
         <v>-10.0824593392167</v>
       </c>
-      <c r="T23">
+      <c r="U23">
         <v>-1.43705701828003</v>
       </c>
-      <c r="U23">
+      <c r="V23">
         <v>14.0086354022318</v>
       </c>
-      <c r="V23">
+      <c r="W23">
         <v>18637541110.4777</v>
       </c>
-      <c r="W23">
+      <c r="X23">
         <v>3.28531568230903</v>
       </c>
-      <c r="X23">
+      <c r="Y23">
         <v>45.2556341623514</v>
       </c>
-      <c r="Y23">
+      <c r="Z23">
         <v>11.849</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:26">
       <c r="A24" s="1">
         <v>2012</v>
       </c>
@@ -1955,55 +2027,58 @@
         <v>211100000</v>
       </c>
       <c r="J24">
+        <v>279116666666.667</v>
+      </c>
+      <c r="K24">
         <v>2.22619979863525</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>2996.0677072015</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>28.3</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>11.1781214545889</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>28.6894966262614</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>20.2282199796979</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>24.3148026512211</v>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <v>7.11172943343081</v>
       </c>
-      <c r="R24">
+      <c r="S24">
         <v>19.4397903688734</v>
       </c>
-      <c r="S24">
+      <c r="T24">
         <v>-10.0051949602914</v>
       </c>
-      <c r="T24">
+      <c r="U24">
         <v>-1.43632972240448</v>
       </c>
-      <c r="U24">
+      <c r="V24">
         <v>12.3849047590613</v>
       </c>
-      <c r="V24">
+      <c r="W24">
         <v>15672467970.7728</v>
       </c>
-      <c r="W24">
+      <c r="X24">
         <v>2.48779534146603</v>
       </c>
-      <c r="X24">
+      <c r="Y24">
         <v>40.7117692721084</v>
       </c>
-      <c r="Y24">
+      <c r="Z24">
         <v>12.597</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:26">
       <c r="A25" s="1">
         <v>2013</v>
       </c>
@@ -2029,52 +2104,55 @@
         <v>301000000</v>
       </c>
       <c r="J25">
+        <v>288434108527.132</v>
+      </c>
+      <c r="K25">
         <v>2.18546605362143</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>3025.52563552448</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>11.3523973339067</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>32.2017308105784</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>21.4163083207912</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>23.3551924317351</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <v>9.46971981064917</v>
       </c>
-      <c r="R25">
+      <c r="S25">
         <v>22.5897666592664</v>
       </c>
-      <c r="S25">
+      <c r="T25">
         <v>-12.6356159965599</v>
       </c>
-      <c r="T25">
+      <c r="U25">
         <v>-1.63883090019226</v>
       </c>
-      <c r="U25">
+      <c r="V25">
         <v>13.4980649322726</v>
       </c>
-      <c r="V25">
+      <c r="W25">
         <v>16536236826.4074</v>
       </c>
-      <c r="W25">
+      <c r="X25">
         <v>2.73003963526374</v>
       </c>
-      <c r="X25">
+      <c r="Y25">
         <v>40.373038056332</v>
       </c>
-      <c r="Y25">
+      <c r="Z25">
         <v>13.154</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:26">
       <c r="A26" s="1">
         <v>2014</v>
       </c>
@@ -2100,52 +2178,55 @@
         <v>252700000</v>
       </c>
       <c r="J26">
+        <v>305595408895.265</v>
+      </c>
+      <c r="K26">
         <v>2.91591187985748</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>3133.39102265541</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>11.849765258216</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>32.9206291079812</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>19.8767136150235</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>22.6760563380282</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <v>10.0702154687481</v>
       </c>
-      <c r="R26">
+      <c r="S26">
         <v>22.7221711517273</v>
       </c>
-      <c r="S26">
+      <c r="T26">
         <v>-11.0277183098592</v>
       </c>
-      <c r="T26">
+      <c r="U26">
         <v>-1.63117659091949</v>
       </c>
-      <c r="U26">
+      <c r="V26">
         <v>12.2201408450704</v>
       </c>
-      <c r="V26">
+      <c r="W26">
         <v>14926998051.7397</v>
       </c>
-      <c r="W26">
+      <c r="X26">
         <v>2.21204888604566</v>
       </c>
-      <c r="X26">
+      <c r="Y26">
         <v>36.9201877934272</v>
       </c>
-      <c r="Y26">
+      <c r="Z26">
         <v>13.105</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:26">
       <c r="A27" s="1">
         <v>2015</v>
       </c>
@@ -2171,55 +2252,58 @@
         <v>181700000</v>
       </c>
       <c r="J27">
+        <v>329366576819.407</v>
+      </c>
+      <c r="K27">
         <v>4.37201907790141</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>3306.98159414141</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>31.8</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>11.7598919759401</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>30.2303694913867</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>20.9886247391464</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>21.6620974671631</v>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <v>10.370490343517</v>
       </c>
-      <c r="R27">
+      <c r="S27">
         <v>24.2332160259881</v>
       </c>
-      <c r="S27">
+      <c r="T27">
         <v>-10.7275665943778</v>
       </c>
-      <c r="T27">
+      <c r="U27">
         <v>-1.49933218955994</v>
       </c>
-      <c r="U27">
+      <c r="V27">
         <v>12.5192110970171</v>
       </c>
-      <c r="V27">
+      <c r="W27">
         <v>15858887325.7756</v>
       </c>
-      <c r="W27">
+      <c r="X27">
         <v>2.59707505474829</v>
       </c>
-      <c r="X27">
+      <c r="Y27">
         <v>34.8459429600229</v>
       </c>
-      <c r="Y27">
+      <c r="Z27">
         <v>13.052</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:26">
       <c r="A28" s="1">
         <v>2016</v>
       </c>
@@ -2245,37 +2329,40 @@
         <v>206600000</v>
       </c>
       <c r="J28">
+        <v>332441717791.411</v>
+      </c>
+      <c r="K28">
         <v>4.34664345555447</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>3270.6287768197</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>11.4268841809995</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>19.9010851110947</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <v>13.813606214829</v>
       </c>
-      <c r="T28">
+      <c r="U28">
         <v>-1.43972682952881</v>
       </c>
-      <c r="V28">
+      <c r="W28">
         <v>23642691705.9678</v>
       </c>
-      <c r="W28">
+      <c r="X28">
         <v>3.88541069587349</v>
       </c>
-      <c r="X28">
+      <c r="Y28">
         <v>30.2465490514505</v>
       </c>
-      <c r="Y28">
+      <c r="Z28">
         <v>12.45</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:26">
       <c r="A29" s="1">
         <v>2017</v>
       </c>
@@ -2301,40 +2388,43 @@
         <v>199000000</v>
       </c>
       <c r="J29">
+        <v>248362771739.13</v>
+      </c>
+      <c r="K29">
         <v>4.18122099994778</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>2395.10333299491</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>31.5</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>9.57903662572827</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>27.8180475395935</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <v>29.5066083940039</v>
       </c>
-      <c r="T29">
+      <c r="U29">
         <v>-1.42964589595795</v>
       </c>
-      <c r="V29">
+      <c r="W29">
         <v>36400242555.8255</v>
       </c>
-      <c r="W29">
+      <c r="X29">
         <v>5.72306111855628</v>
       </c>
-      <c r="X29">
+      <c r="Y29">
         <v>42.8321343581608</v>
       </c>
-      <c r="Y29">
+      <c r="Z29">
         <v>11.767</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:26">
       <c r="A30" s="1">
         <v>2018</v>
       </c>
@@ -2360,37 +2450,40 @@
         <v>323489000</v>
       </c>
       <c r="J30">
+        <v>262588632526.73</v>
+      </c>
+      <c r="K30">
         <v>5.3311086189448</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>2484.70315630508</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>7.94222279370794</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>27.9263640649779</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>14.4014657807422</v>
       </c>
-      <c r="T30">
+      <c r="U30">
         <v>-1.18812155723572</v>
       </c>
-      <c r="V30">
+      <c r="W30">
         <v>41839242990.7097</v>
       </c>
-      <c r="W30">
+      <c r="X30">
         <v>5.85734270401284</v>
       </c>
-      <c r="X30">
+      <c r="Y30">
         <v>45.9110196733959</v>
       </c>
-      <c r="Y30">
+      <c r="Z30">
         <v>9.855</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:26">
       <c r="A31" s="1">
         <v>2019</v>
       </c>
@@ -2416,40 +2509,43 @@
         <v>405032000</v>
       </c>
       <c r="J31">
+        <v>318678815489.749</v>
+      </c>
+      <c r="K31">
         <v>5.55209307156956</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>2962.98892023003</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>31.9</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>7.2855611150822</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>24.4799857040743</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <v>9.152799593248041</v>
       </c>
-      <c r="T31">
+      <c r="U31">
         <v>-1.12463080883026</v>
       </c>
-      <c r="V31">
+      <c r="W31">
         <v>44568837112.0669</v>
       </c>
-      <c r="W31">
+      <c r="X31">
         <v>5.83923947440236</v>
       </c>
-      <c r="X31">
+      <c r="Y31">
         <v>41.1240171551108</v>
       </c>
-      <c r="Y31">
+      <c r="Z31">
         <v>7.851</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:26">
       <c r="A32" s="1">
         <v>2020</v>
       </c>
@@ -2475,37 +2571,40 @@
         <v>326500000</v>
       </c>
       <c r="J32">
+        <v>383817841547.099</v>
+      </c>
+      <c r="K32">
         <v>3.55016483786838</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>3511.11381026379</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>7.5399018301206</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>19.6534798296655</v>
       </c>
-      <c r="Q32">
+      <c r="R32">
         <v>5.04493288977539</v>
       </c>
-      <c r="T32">
+      <c r="U32">
         <v>-1.18193280696869</v>
       </c>
-      <c r="V32">
+      <c r="W32">
         <v>38972812936.6708</v>
       </c>
-      <c r="W32">
+      <c r="X32">
         <v>5.56473451430895</v>
       </c>
-      <c r="X32">
+      <c r="Y32">
         <v>32.1262555667523</v>
       </c>
-      <c r="Y32">
+      <c r="Z32">
         <v>7.974</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:26">
       <c r="A33" s="1">
         <v>2021</v>
       </c>
@@ -2531,40 +2630,43 @@
         <v>367000000</v>
       </c>
       <c r="J33">
+        <v>424671765455.704</v>
+      </c>
+      <c r="K33">
         <v>3.29064601202211</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>3827.35415374308</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>28.5</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>7.55804355330102</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>19.295823265447</v>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <v>5.21404940513041</v>
       </c>
-      <c r="T33">
+      <c r="U33">
         <v>-1.0328643321991</v>
       </c>
-      <c r="V33">
+      <c r="W33">
         <v>39824388217.3615</v>
       </c>
-      <c r="W33">
+      <c r="X33">
         <v>4.38225643427728</v>
       </c>
-      <c r="X33">
+      <c r="Y33">
         <v>29.8569734808122</v>
       </c>
-      <c r="Y33">
+      <c r="Z33">
         <v>7.441</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:26">
       <c r="A34" s="1">
         <v>2022</v>
       </c>
@@ -2590,37 +2692,40 @@
         <v>341800000</v>
       </c>
       <c r="J34">
+        <v>476747720364.742</v>
+      </c>
+      <c r="K34">
         <v>6.58784560886967</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>4233.30783744856</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>7.26809053235575</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>21.8960790564233</v>
       </c>
-      <c r="Q34">
+      <c r="R34">
         <v>13.8956609775178</v>
       </c>
-      <c r="T34">
+      <c r="U34">
         <v>-0.978700578212738</v>
       </c>
-      <c r="V34">
+      <c r="W34">
         <v>32143926008.4607</v>
       </c>
-      <c r="W34">
+      <c r="X34">
         <v>3.32738146369502</v>
       </c>
-      <c r="X34">
+      <c r="Y34">
         <v>36.9831048772713</v>
       </c>
-      <c r="Y34">
+      <c r="Z34">
         <v>7.344</v>
       </c>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:26">
       <c r="A35" s="1">
         <v>2023</v>
       </c>
@@ -2646,37 +2751,40 @@
         <v>390400000</v>
       </c>
       <c r="J35">
+        <v>395926075163.006</v>
+      </c>
+      <c r="K35">
         <v>3.76028052279247</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>3456.78968456253</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>6.78850660732221</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
         <v>21.3443094314355</v>
       </c>
-      <c r="Q35">
+      <c r="R35">
         <v>33.8847763115546</v>
       </c>
-      <c r="T35">
+      <c r="U35">
         <v>-0.8667643070220949</v>
       </c>
-      <c r="V35">
+      <c r="W35">
         <v>33070180836.1374</v>
       </c>
-      <c r="W35">
+      <c r="X35">
         <v>3.87390992001782</v>
       </c>
-      <c r="X35">
+      <c r="Y35">
         <v>40.4504007720031</v>
       </c>
-      <c r="Y35">
+      <c r="Z35">
         <v>7.334</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:26">
       <c r="A36" s="1">
         <v>2024</v>
       </c>
@@ -2693,30 +2801,33 @@
         <v>508200000</v>
       </c>
       <c r="J36">
+        <v>389059911003.566</v>
+      </c>
+      <c r="K36">
         <v>2.3991692678251</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>3338.47371395895</v>
       </c>
-      <c r="M36">
+      <c r="N36">
         <v>6.27031988169153</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
         <v>23.2245098772607</v>
       </c>
-      <c r="Q36">
+      <c r="R36">
         <v>28.2705899322083</v>
       </c>
-      <c r="V36">
+      <c r="W36">
         <v>44921341018.4659</v>
       </c>
-      <c r="W36">
+      <c r="X36">
         <v>4.53950764706678</v>
       </c>
-      <c r="X36">
+      <c r="Y36">
         <v>39.6007520873733</v>
       </c>
-      <c r="Y36">
+      <c r="Z36">
         <v>7.198</v>
       </c>
     </row>

--- a/EGY_WB_timeseries.xlsx
+++ b/EGY_WB_timeseries.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beldjenna/Desktop/Rating Algo/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76BC433-3F3D-5D47-9F70-1E4E9EBBE5A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -73,8 +67,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,18 +85,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -132,33 +120,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -196,7 +175,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -230,7 +209,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -265,10 +243,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -441,11 +418,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -495,86 +472,77 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
       <c r="B2">
-        <v>-0.49266779422759999</v>
+        <v>-0.4926677942276</v>
       </c>
       <c r="C2">
-        <v>-0.97257027344898594</v>
+        <v>-0.9725702734489859</v>
       </c>
       <c r="D2">
         <v>71.7</v>
       </c>
       <c r="E2">
-        <v>16.201117318435799</v>
+        <v>16.2011173184358</v>
       </c>
       <c r="F2">
-        <v>6.3700038299176596</v>
+        <v>6.37000382991766</v>
       </c>
       <c r="G2">
         <v>1366.09274372613</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
       <c r="J2">
-        <v>22.816818582769798</v>
+        <v>22.8168185827698</v>
       </c>
       <c r="K2">
         <v>2.8</v>
       </c>
-      <c r="L2" s="2"/>
       <c r="M2">
         <v>1.3</v>
       </c>
       <c r="N2">
-        <v>4.9797523766756099E-2</v>
-      </c>
-      <c r="O2" s="2"/>
+        <v>0.0497975237667561</v>
+      </c>
       <c r="P2">
-        <v>39.017935901205497</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+        <v>39.0179359012055</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3" s="2"/>
       <c r="C3">
-        <v>-0.40171842765542198</v>
+        <v>-0.401718427655422</v>
       </c>
       <c r="D3">
-        <v>79.099999999999994</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="E3">
-        <v>17.479788123780299</v>
+        <v>17.4797881237803</v>
       </c>
       <c r="F3">
-        <v>3.5352519739150701</v>
+        <v>3.53525197391507</v>
       </c>
       <c r="G3">
-        <v>1295.1374184163001</v>
-      </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
+        <v>1295.1374184163</v>
+      </c>
       <c r="J3">
-        <v>22.330638416504001</v>
+        <v>22.330638416504</v>
       </c>
       <c r="K3">
         <v>2.4</v>
       </c>
-      <c r="L3" s="2"/>
       <c r="M3">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="O3" s="2"/>
+        <v>-1.1</v>
+      </c>
       <c r="P3">
-        <v>39.810426540284404</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+        <v>39.8104265402844</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
@@ -582,7 +550,7 @@
         <v>-0.44015771150589</v>
       </c>
       <c r="C4">
-        <v>0.73097915017154902</v>
+        <v>0.730979150171549</v>
       </c>
       <c r="D4">
         <v>85.8</v>
@@ -591,25 +559,25 @@
         <v>18.3161784111903</v>
       </c>
       <c r="F4">
-        <v>2.3902040257372601</v>
+        <v>2.39020402573726</v>
       </c>
       <c r="G4">
-        <v>1116.8288462621299</v>
+        <v>1116.82884626213</v>
       </c>
       <c r="H4">
         <v>27.2483504882555</v>
       </c>
       <c r="I4">
-        <v>24.349696489839001</v>
+        <v>24.349696489839</v>
       </c>
       <c r="J4">
-        <v>22.670889416732599</v>
+        <v>22.6708894167326</v>
       </c>
       <c r="K4">
-        <v>2.2999999999999998</v>
+        <v>2.3</v>
       </c>
       <c r="L4">
-        <v>19.665065282244001</v>
+        <v>19.665065282244</v>
       </c>
       <c r="M4">
         <v>-6.74531538664555</v>
@@ -624,7 +592,7 @@
         <v>40.9870678279229</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
@@ -632,28 +600,28 @@
         <v>-0.530747950077057</v>
       </c>
       <c r="C5">
-        <v>4.6623137724550903</v>
+        <v>4.66231377245509</v>
       </c>
       <c r="D5">
-        <v>97.1</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="E5">
-        <v>21.796407185628698</v>
+        <v>21.7964071856287</v>
       </c>
       <c r="F5">
-        <v>3.1934547373974498</v>
+        <v>3.19345473739745</v>
       </c>
       <c r="G5">
-        <v>1031.2755629128401</v>
+        <v>1031.27556291284</v>
       </c>
       <c r="H5">
         <v>27.3324550898204</v>
       </c>
       <c r="I5">
-        <v>25.431137724550901</v>
+        <v>25.4311377245509</v>
       </c>
       <c r="J5">
-        <v>24.383233532934099</v>
+        <v>24.3832335329341</v>
       </c>
       <c r="K5">
         <v>3.4</v>
@@ -662,7 +630,7 @@
         <v>20.7925477377687</v>
       </c>
       <c r="M5">
-        <v>-5.8162874251497003</v>
+        <v>-5.8162874251497</v>
       </c>
       <c r="N5">
         <v>-0.640924513339996</v>
@@ -671,65 +639,65 @@
         <v>13.3499401197605</v>
       </c>
       <c r="P5">
-        <v>46.179640718562901</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+        <v>46.1796407185629</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
       <c r="B6">
-        <v>-0.58350574970245395</v>
+        <v>-0.5835057497024539</v>
       </c>
       <c r="C6">
-        <v>4.9778841953430897</v>
+        <v>4.97788419534309</v>
       </c>
       <c r="D6">
         <v>96.5</v>
       </c>
       <c r="E6">
-        <v>28.229960848959401</v>
+        <v>28.2299608489594</v>
       </c>
       <c r="F6">
-        <v>4.0920716112533997</v>
+        <v>4.0920716112534</v>
       </c>
       <c r="G6">
-        <v>991.25568914525297</v>
+        <v>991.255689145253</v>
       </c>
       <c r="H6">
-        <v>26.890377086338301</v>
+        <v>26.8903770863383</v>
       </c>
       <c r="I6">
-        <v>24.640428600865398</v>
+        <v>24.6404286008654</v>
       </c>
       <c r="J6">
         <v>29.5899443643107</v>
       </c>
       <c r="K6">
-        <v>8.1999999999999993</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L6">
-        <v>21.085985333220901</v>
+        <v>21.0859853332209</v>
       </c>
       <c r="M6">
         <v>-5.61055017514939</v>
       </c>
       <c r="N6">
-        <v>-0.82240170240402199</v>
+        <v>-0.822401702404022</v>
       </c>
       <c r="O6">
         <v>13.8359777457243</v>
       </c>
       <c r="P6">
-        <v>57.819905213270097</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+        <v>57.8199052132701</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
       <c r="B7">
-        <v>-0.53949952125549305</v>
+        <v>-0.5394995212554931</v>
       </c>
       <c r="C7">
         <v>2.34529559888579</v>
@@ -738,110 +706,110 @@
         <v>98.3</v>
       </c>
       <c r="E7">
-        <v>30.343546889507898</v>
+        <v>30.3435468895079</v>
       </c>
       <c r="F7">
-        <v>4.4717444717443398</v>
+        <v>4.47174447174434</v>
       </c>
       <c r="G7">
-        <v>1105.5392071390299</v>
+        <v>1105.53920713903</v>
       </c>
       <c r="H7">
-        <v>27.388857938718701</v>
+        <v>27.3888579387187</v>
       </c>
       <c r="I7">
         <v>24.2916620241411</v>
       </c>
       <c r="J7">
-        <v>32.609099350046399</v>
+        <v>32.6090993500464</v>
       </c>
       <c r="K7">
-        <v>8.6999999999999993</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L7">
-        <v>20.208964736353199</v>
+        <v>20.2089647363532</v>
       </c>
       <c r="M7">
-        <v>-6.4488579387186604</v>
+        <v>-6.44885793871866</v>
       </c>
       <c r="N7">
-        <v>-0.62935864925384499</v>
+        <v>-0.629358649253845</v>
       </c>
       <c r="O7">
-        <v>14.068635097493001</v>
+        <v>14.068635097493</v>
       </c>
       <c r="P7">
-        <v>62.952646239554298</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+        <v>62.9526462395543</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
       <c r="B8">
-        <v>-0.73733407258987405</v>
+        <v>-0.737334072589874</v>
       </c>
       <c r="C8">
-        <v>2.4532216286223099</v>
+        <v>2.45322162862231</v>
       </c>
       <c r="D8">
-        <v>85.9</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="E8">
-        <v>29.949813825481598</v>
+        <v>29.9498138254816</v>
       </c>
       <c r="F8">
-        <v>6.8438381937911696</v>
+        <v>6.84383819379117</v>
       </c>
       <c r="G8">
         <v>1298.97900203124</v>
       </c>
       <c r="H8">
-        <v>32.763671685284102</v>
+        <v>32.7636716852841</v>
       </c>
       <c r="I8">
-        <v>28.138983325238801</v>
+        <v>28.1389833252388</v>
       </c>
       <c r="J8">
-        <v>31.568722680913101</v>
+        <v>31.5687226809131</v>
       </c>
       <c r="K8">
         <v>4.3</v>
       </c>
       <c r="L8">
-        <v>17.201054248121899</v>
+        <v>17.2010542481219</v>
       </c>
       <c r="M8">
-        <v>-7.1684960336732999</v>
+        <v>-7.1684960336733</v>
       </c>
       <c r="N8">
-        <v>-0.83780765533447299</v>
+        <v>-0.837807655334473</v>
       </c>
       <c r="O8">
         <v>15.8295127084345</v>
       </c>
       <c r="P8">
-        <v>61.518536506394703</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+        <v>61.5185365063947</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
       <c r="B9">
-        <v>-0.73787009716033902</v>
+        <v>-0.737870097160339</v>
       </c>
       <c r="C9">
-        <v>0.31555263157894697</v>
+        <v>0.315552631578947</v>
       </c>
       <c r="D9">
         <v>76.3</v>
       </c>
       <c r="E9">
-        <v>30.249731471535998</v>
+        <v>30.249731471536</v>
       </c>
       <c r="F9">
-        <v>7.0878274268103798</v>
+        <v>7.08782742681038</v>
       </c>
       <c r="G9">
         <v>1547.74170735909</v>
@@ -850,39 +818,39 @@
         <v>29.3352309344791</v>
       </c>
       <c r="I9">
-        <v>27.117091836734701</v>
+        <v>27.1170918367347</v>
       </c>
       <c r="J9">
-        <v>34.828141783028997</v>
+        <v>34.828141783029</v>
       </c>
       <c r="K9">
         <v>10.9</v>
       </c>
       <c r="L9">
-        <v>17.560305150653001</v>
+        <v>17.560305150653</v>
       </c>
       <c r="M9">
-        <v>-4.5579618689581096</v>
+        <v>-4.55796186895811</v>
       </c>
       <c r="N9">
         <v>-0.552382111549377</v>
       </c>
       <c r="O9">
-        <v>15.349852309344801</v>
+        <v>15.3498523093448</v>
       </c>
       <c r="P9">
-        <v>65.077873254565006</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+        <v>65.07787325456501</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
       <c r="B10">
-        <v>-0.76590925455093395</v>
+        <v>-0.7659092545509339</v>
       </c>
       <c r="C10">
-        <v>-0.86882188721384701</v>
+        <v>-0.868821887213847</v>
       </c>
       <c r="D10">
         <v>66.8</v>
@@ -891,10 +859,10 @@
         <v>33.0429927414852</v>
       </c>
       <c r="F10">
-        <v>7.1562835660581898</v>
+        <v>7.15628356605819</v>
       </c>
       <c r="G10">
-        <v>1896.2159426977901</v>
+        <v>1896.21594269779</v>
       </c>
       <c r="H10">
         <v>30.3182043551089</v>
@@ -903,7 +871,7 @@
         <v>27.6239352317141</v>
       </c>
       <c r="J10">
-        <v>38.637632607481898</v>
+        <v>38.6376326074819</v>
       </c>
       <c r="K10">
         <v>11.7</v>
@@ -912,24 +880,24 @@
         <v>15.0853305376009</v>
       </c>
       <c r="M10">
-        <v>-6.3607906197654902</v>
+        <v>-6.36079061976549</v>
       </c>
       <c r="N10">
-        <v>-0.51043170690536499</v>
+        <v>-0.510431706905365</v>
       </c>
       <c r="O10">
         <v>15.3205248464545</v>
       </c>
       <c r="P10">
-        <v>71.680625348967098</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+        <v>71.6806253489671</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
       <c r="B11">
-        <v>-0.46486279368400601</v>
+        <v>-0.464862793684006</v>
       </c>
       <c r="C11">
         <v>-1.7707391095759</v>
@@ -938,101 +906,101 @@
         <v>69.5</v>
       </c>
       <c r="E11">
-        <v>24.956822107081202</v>
+        <v>24.9568221070812</v>
       </c>
       <c r="F11">
-        <v>4.6735997995239096</v>
+        <v>4.67359979952391</v>
       </c>
       <c r="G11">
-        <v>2161.6396457392698</v>
+        <v>2161.63964573927</v>
       </c>
       <c r="H11">
-        <v>30.077125311840302</v>
+        <v>30.0771253118403</v>
       </c>
       <c r="I11">
         <v>26.9200729226636</v>
       </c>
       <c r="J11">
-        <v>31.596622529265002</v>
+        <v>31.596622529265</v>
       </c>
       <c r="K11">
         <v>16.2</v>
       </c>
       <c r="L11">
-        <v>13.958581501276999</v>
+        <v>13.958581501277</v>
       </c>
       <c r="M11">
-        <v>-6.5629629629629598</v>
+        <v>-6.56296296296296</v>
       </c>
       <c r="N11">
-        <v>-0.60722708702087402</v>
+        <v>-0.607227087020874</v>
       </c>
       <c r="O11">
-        <v>15.661360583381301</v>
+        <v>15.6613605833813</v>
       </c>
       <c r="P11">
         <v>56.5534446363462</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
       <c r="B12">
-        <v>-0.59687185287475597</v>
+        <v>-0.596871852874756</v>
       </c>
       <c r="C12">
-        <v>-2.0566830764130599</v>
+        <v>-2.05668307641306</v>
       </c>
       <c r="D12">
-        <v>69.599999999999994</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E12">
-        <v>21.349245814685901</v>
+        <v>21.3492458146859</v>
       </c>
       <c r="F12">
-        <v>5.1472348575530997</v>
+        <v>5.1472348575531</v>
       </c>
       <c r="G12">
-        <v>2455.0819464528199</v>
+        <v>2455.08194645282</v>
       </c>
       <c r="H12">
         <v>28.8602519476214</v>
       </c>
       <c r="I12">
-        <v>24.783822310624899</v>
+        <v>24.7838223106249</v>
       </c>
       <c r="J12">
-        <v>26.587104259903899</v>
+        <v>26.5871042599039</v>
       </c>
       <c r="K12">
         <v>11.7</v>
       </c>
       <c r="L12">
-        <v>17.861583710433202</v>
+        <v>17.8615837104332</v>
       </c>
       <c r="M12">
-        <v>-7.7339134758826402</v>
+        <v>-7.73391347588264</v>
       </c>
       <c r="N12">
-        <v>-0.89841830730438199</v>
+        <v>-0.898418307304382</v>
       </c>
       <c r="O12">
         <v>14.1300762473065</v>
       </c>
       <c r="P12">
-        <v>47.936350074589797</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+        <v>47.9363500745898</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
       <c r="B13">
-        <v>-0.63326394557952903</v>
+        <v>-0.633263945579529</v>
       </c>
       <c r="C13">
-        <v>-2.3237881263219302</v>
+        <v>-2.32378812632193</v>
       </c>
       <c r="D13">
         <v>72.8</v>
@@ -1041,28 +1009,28 @@
         <v>20.5674276128656</v>
       </c>
       <c r="F13">
-        <v>1.7645719489981999</v>
+        <v>1.7645719489982</v>
       </c>
       <c r="G13">
-        <v>2590.6438489196498</v>
+        <v>2590.64384891965</v>
       </c>
       <c r="H13">
-        <v>29.189927795200902</v>
+        <v>29.1899277952009</v>
       </c>
       <c r="I13">
         <v>21.9307417402086</v>
       </c>
       <c r="J13">
-        <v>24.688206549485798</v>
+        <v>24.6882065494858</v>
       </c>
       <c r="K13">
         <v>10.0649259874818</v>
       </c>
       <c r="L13">
-        <v>19.079808236955799</v>
+        <v>19.0798082369558</v>
       </c>
       <c r="M13">
-        <v>-10.082459339216699</v>
+        <v>-10.0824593392167</v>
       </c>
       <c r="N13">
         <v>-1.43705701828003</v>
@@ -1071,42 +1039,42 @@
         <v>14.0086354022318</v>
       </c>
       <c r="P13">
-        <v>45.255634162351399</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+        <v>45.2556341623514</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
       <c r="B14">
-        <v>-0.57966434955596902</v>
+        <v>-0.579664349555969</v>
       </c>
       <c r="C14">
         <v>-2.49788021735236</v>
       </c>
       <c r="D14">
-        <v>69.900000000000006</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E14">
-        <v>16.396966620887302</v>
+        <v>16.3969666208873</v>
       </c>
       <c r="F14">
-        <v>2.2261997986352502</v>
+        <v>2.22619979863525</v>
       </c>
       <c r="G14">
-        <v>2996.0677072015001</v>
+        <v>2996.0677072015</v>
       </c>
       <c r="H14">
-        <v>28.689496626261398</v>
+        <v>28.6894966262614</v>
       </c>
       <c r="I14">
-        <v>20.228219979697901</v>
+        <v>20.2282199796979</v>
       </c>
       <c r="J14">
         <v>24.3148026512211</v>
       </c>
       <c r="K14">
-        <v>7.1117294334308099</v>
+        <v>7.11172943343081</v>
       </c>
       <c r="L14">
         <v>19.4397903688734</v>
@@ -1121,51 +1089,51 @@
         <v>12.3849047590613</v>
       </c>
       <c r="P14">
-        <v>40.711769272108398</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+        <v>40.7117692721084</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
       <c r="B15">
-        <v>-0.61410206556320202</v>
+        <v>-0.614102065563202</v>
       </c>
       <c r="C15">
-        <v>-1.2251324983874401</v>
+        <v>-1.22513249838744</v>
       </c>
       <c r="D15">
         <v>79.8</v>
       </c>
       <c r="E15">
-        <v>17.017845624596902</v>
+        <v>17.0178456245969</v>
       </c>
       <c r="F15">
-        <v>2.1854660536214299</v>
+        <v>2.18546605362143</v>
       </c>
       <c r="G15">
-        <v>3025.5256355244801</v>
+        <v>3025.52563552448</v>
       </c>
       <c r="H15">
-        <v>32.201730810578397</v>
+        <v>32.2017308105784</v>
       </c>
       <c r="I15">
-        <v>21.416308320791199</v>
+        <v>21.4163083207912</v>
       </c>
       <c r="J15">
-        <v>23.355192431735102</v>
+        <v>23.3551924317351</v>
       </c>
       <c r="K15">
-        <v>9.4697198106491705</v>
+        <v>9.46971981064917</v>
       </c>
       <c r="L15">
-        <v>22.589766659266399</v>
+        <v>22.5897666592664</v>
       </c>
       <c r="M15">
-        <v>-12.635615996559901</v>
+        <v>-12.6356159965599</v>
       </c>
       <c r="N15">
-        <v>-1.6388309001922601</v>
+        <v>-1.63883090019226</v>
       </c>
       <c r="O15">
         <v>13.4980649322726</v>
@@ -1174,42 +1142,42 @@
         <v>40.373038056332</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
       <c r="B16">
-        <v>-0.57551801204681396</v>
+        <v>-0.575518012046814</v>
       </c>
       <c r="C16">
-        <v>-1.9484913145539899</v>
+        <v>-1.94849131455399</v>
       </c>
       <c r="D16">
-        <v>80.900000000000006</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E16">
-        <v>14.244131455399099</v>
+        <v>14.2441314553991</v>
       </c>
       <c r="F16">
-        <v>2.9159118798574801</v>
+        <v>2.91591187985748</v>
       </c>
       <c r="G16">
-        <v>3133.3910226554099</v>
+        <v>3133.39102265541</v>
       </c>
       <c r="H16">
-        <v>32.920629107981199</v>
+        <v>32.9206291079812</v>
       </c>
       <c r="I16">
-        <v>19.876713615023501</v>
+        <v>19.8767136150235</v>
       </c>
       <c r="J16">
         <v>22.6760563380282</v>
       </c>
       <c r="K16">
-        <v>10.070215468748099</v>
+        <v>10.0702154687481</v>
       </c>
       <c r="L16">
-        <v>22.722171151727299</v>
+        <v>22.7221711517273</v>
       </c>
       <c r="M16">
         <v>-11.0277183098592</v>
@@ -1221,36 +1189,36 @@
         <v>12.2201408450704</v>
       </c>
       <c r="P16">
-        <v>36.920187793427203</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+        <v>36.9201877934272</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
       <c r="B17">
-        <v>-0.60090672969818104</v>
+        <v>-0.600906729698181</v>
       </c>
       <c r="C17">
-        <v>-5.2352913785343098</v>
+        <v>-5.23529137853431</v>
       </c>
       <c r="D17">
         <v>83.8</v>
       </c>
       <c r="E17">
-        <v>13.183845492859801</v>
+        <v>13.1838454928598</v>
       </c>
       <c r="F17">
-        <v>4.3720190779014096</v>
+        <v>4.37201907790141</v>
       </c>
       <c r="G17">
-        <v>3306.9815941414099</v>
+        <v>3306.98159414141</v>
       </c>
       <c r="H17">
         <v>30.2303694913867</v>
       </c>
       <c r="I17">
-        <v>20.988624739146399</v>
+        <v>20.9886247391464</v>
       </c>
       <c r="J17">
         <v>21.6620974671631</v>
@@ -1259,195 +1227,179 @@
         <v>10.370490343517</v>
       </c>
       <c r="L17">
-        <v>24.233216025988099</v>
+        <v>24.2332160259881</v>
       </c>
       <c r="M17">
         <v>-10.7275665943778</v>
       </c>
       <c r="N17">
-        <v>-1.4993321895599401</v>
+        <v>-1.49933218955994</v>
       </c>
       <c r="O17">
         <v>12.5192110970171</v>
       </c>
       <c r="P17">
-        <v>34.845942960022903</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+        <v>34.8459429600229</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
       <c r="B18">
-        <v>-0.59089314937591597</v>
+        <v>-0.590893149375916</v>
       </c>
       <c r="C18">
-        <v>-6.1646595187126296</v>
+        <v>-6.16465951871263</v>
       </c>
       <c r="D18">
-        <v>91.6</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="E18">
-        <v>10.345463940355801</v>
+        <v>10.3454639403558</v>
       </c>
       <c r="F18">
         <v>4.34664345555447</v>
       </c>
       <c r="G18">
-        <v>3270.6287768196999</v>
-      </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
+        <v>3270.6287768197</v>
+      </c>
       <c r="J18">
-        <v>19.901085111094702</v>
+        <v>19.9010851110947</v>
       </c>
       <c r="K18">
-        <v>13.813606214829001</v>
-      </c>
-      <c r="L18" s="2"/>
+        <v>13.813606214829</v>
+      </c>
       <c r="M18">
         <v>-11.8</v>
       </c>
       <c r="N18">
-        <v>-1.4397268295288099</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>-1.43972682952881</v>
+      </c>
       <c r="P18">
-        <v>30.246549051450501</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+        <v>30.2465490514505</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
       <c r="B19">
-        <v>-0.49598234891891502</v>
+        <v>-0.495982348918915</v>
       </c>
       <c r="C19">
-        <v>-3.1968156678246098</v>
+        <v>-3.19681566782461</v>
       </c>
       <c r="D19">
         <v>97.8</v>
       </c>
       <c r="E19">
-        <v>15.014086818567201</v>
+        <v>15.0140868185672</v>
       </c>
       <c r="F19">
-        <v>4.1812209999477803</v>
+        <v>4.18122099994778</v>
       </c>
       <c r="G19">
         <v>2395.10333299491</v>
       </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
       <c r="J19">
-        <v>27.818047539593501</v>
+        <v>27.8180475395935</v>
       </c>
       <c r="K19">
-        <v>29.506608394003901</v>
-      </c>
-      <c r="L19" s="2"/>
+        <v>29.5066083940039</v>
+      </c>
       <c r="M19">
         <v>-9.9</v>
       </c>
       <c r="N19">
-        <v>-1.4296458959579501</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>-1.42964589595795</v>
+      </c>
       <c r="P19">
-        <v>42.832134358160801</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+        <v>42.8321343581608</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
       <c r="B20">
-        <v>-0.51472234725952104</v>
+        <v>-0.514722347259521</v>
       </c>
       <c r="C20">
-        <v>-2.9316448371197801</v>
+        <v>-2.93164483711978</v>
       </c>
       <c r="D20">
-        <v>87.9</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="E20">
-        <v>17.984655608417999</v>
+        <v>17.984655608418</v>
       </c>
       <c r="F20">
-        <v>5.3311086189447998</v>
+        <v>5.3311086189448</v>
       </c>
       <c r="G20">
         <v>2484.70315630508</v>
       </c>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
       <c r="J20">
         <v>27.9263640649779</v>
       </c>
       <c r="K20">
         <v>14.4014657807422</v>
       </c>
-      <c r="L20" s="2"/>
       <c r="M20">
         <v>-9</v>
       </c>
       <c r="N20">
         <v>-1.18812155723572</v>
       </c>
-      <c r="O20" s="2"/>
       <c r="P20">
-        <v>45.911019673395899</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+        <v>45.9110196733959</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
       <c r="B21">
-        <v>-0.65531754493713401</v>
+        <v>-0.655317544937134</v>
       </c>
       <c r="C21">
-        <v>-3.2075854315493801</v>
+        <v>-3.20758543154938</v>
       </c>
       <c r="D21">
-        <v>80.099999999999994</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="E21">
-        <v>16.644031451036501</v>
+        <v>16.6440314510365</v>
       </c>
       <c r="F21">
-        <v>5.5520930715695602</v>
+        <v>5.55209307156956</v>
       </c>
       <c r="G21">
-        <v>2962.9889202300301</v>
-      </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
+        <v>2962.98892023003</v>
+      </c>
       <c r="J21">
-        <v>24.479985704074299</v>
+        <v>24.4799857040743</v>
       </c>
       <c r="K21">
-        <v>9.1527995932480408</v>
-      </c>
-      <c r="L21" s="2"/>
+        <v>9.152799593248041</v>
+      </c>
       <c r="M21">
         <v>-7.6</v>
       </c>
       <c r="N21">
-        <v>-1.1246308088302599</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>-1.12463080883026</v>
+      </c>
       <c r="P21">
-        <v>41.124017155110799</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+        <v>41.1240171551108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
       <c r="B22">
-        <v>-0.81043362617492698</v>
+        <v>-0.810433626174927</v>
       </c>
       <c r="C22">
         <v>-3.70903990583375</v>
@@ -1456,85 +1408,77 @@
         <v>86.2</v>
       </c>
       <c r="E22">
-        <v>12.472775737086801</v>
+        <v>12.4727757370868</v>
       </c>
       <c r="F22">
-        <v>3.5501648378683801</v>
+        <v>3.55016483786838</v>
       </c>
       <c r="G22">
-        <v>3511.1138102637901</v>
-      </c>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
+        <v>3511.11381026379</v>
+      </c>
       <c r="J22">
         <v>19.6534798296655</v>
       </c>
       <c r="K22">
-        <v>5.0449328897753896</v>
-      </c>
-      <c r="L22" s="2"/>
+        <v>5.04493288977539</v>
+      </c>
       <c r="M22">
         <v>-7.5</v>
       </c>
       <c r="N22">
-        <v>-1.1819328069686901</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>-1.18193280696869</v>
+      </c>
       <c r="P22">
-        <v>32.126255566752299</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+        <v>32.1262555667523</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
       <c r="B23">
-        <v>-0.70594334602356001</v>
+        <v>-0.70594334602356</v>
       </c>
       <c r="C23">
-        <v>-4.3824029981200097</v>
+        <v>-4.38240299812001</v>
       </c>
       <c r="D23">
-        <v>89.9</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="E23">
-        <v>10.561150215365201</v>
+        <v>10.5611502153652</v>
       </c>
       <c r="F23">
-        <v>3.2906460120221102</v>
+        <v>3.29064601202211</v>
       </c>
       <c r="G23">
-        <v>3827.3541537430801</v>
-      </c>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
+        <v>3827.35415374308</v>
+      </c>
       <c r="J23">
-        <v>19.295823265447002</v>
+        <v>19.295823265447</v>
       </c>
       <c r="K23">
-        <v>5.2140494051304103</v>
-      </c>
-      <c r="L23" s="2"/>
+        <v>5.21404940513041</v>
+      </c>
       <c r="M23">
         <v>-7</v>
       </c>
       <c r="N23">
         <v>-1.0328643321991</v>
       </c>
-      <c r="O23" s="2"/>
       <c r="P23">
-        <v>29.856973480812201</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+        <v>29.8569734808122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
       <c r="B24">
-        <v>-0.67896217107772805</v>
+        <v>-0.678962171077728</v>
       </c>
       <c r="C24">
-        <v>-2.2100904275198001</v>
+        <v>-2.2100904275198</v>
       </c>
       <c r="D24">
         <v>88.5</v>
@@ -1546,105 +1490,92 @@
         <v>6.58784560886967</v>
       </c>
       <c r="G24">
-        <v>4233.3078374485603</v>
-      </c>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
+        <v>4233.30783744856</v>
+      </c>
       <c r="J24">
         <v>21.8960790564233</v>
       </c>
       <c r="K24">
-        <v>13.895660977517799</v>
-      </c>
-      <c r="L24" s="2"/>
+        <v>13.8956609775178</v>
+      </c>
       <c r="M24">
         <v>-5.7</v>
       </c>
       <c r="N24">
-        <v>-0.97870057821273804</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>-0.978700578212738</v>
+      </c>
       <c r="P24">
-        <v>36.983104877271302</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+        <v>36.9831048772713</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
       <c r="B25">
-        <v>-0.74779039621353105</v>
+        <v>-0.7477903962135311</v>
       </c>
       <c r="C25">
-        <v>-3.1733876007561599</v>
+        <v>-3.17338760075616</v>
       </c>
       <c r="D25">
-        <v>95.9</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="E25">
-        <v>19.106091340567598</v>
+        <v>19.1060913405676</v>
       </c>
       <c r="F25">
         <v>3.76028052279247</v>
       </c>
       <c r="G25">
-        <v>3456.7896845625301</v>
-      </c>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
+        <v>3456.78968456253</v>
+      </c>
       <c r="J25">
-        <v>21.344309431435502</v>
+        <v>21.3443094314355</v>
       </c>
       <c r="K25">
-        <v>33.884776311554603</v>
-      </c>
-      <c r="L25" s="2"/>
+        <v>33.8847763115546</v>
+      </c>
       <c r="M25">
         <v>-5.8</v>
       </c>
       <c r="N25">
-        <v>-0.86676430702209495</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>-0.8667643070220949</v>
+      </c>
       <c r="P25">
         <v>40.4504007720031</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
-      <c r="B26" s="2"/>
       <c r="C26">
-        <v>-5.7204814401440602</v>
+        <v>-5.72048144014406</v>
       </c>
       <c r="D26">
-        <v>90.9</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E26">
-        <v>16.376242210112601</v>
+        <v>16.3762422101126</v>
       </c>
       <c r="F26">
         <v>2.3991692678251</v>
       </c>
       <c r="G26">
-        <v>3338.4737139589502</v>
-      </c>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
+        <v>3338.47371395895</v>
+      </c>
       <c r="J26">
-        <v>23.224509877260701</v>
+        <v>23.2245098772607</v>
       </c>
       <c r="K26">
-        <v>28.270589932208299</v>
-      </c>
-      <c r="L26" s="2"/>
+        <v>28.2705899322083</v>
+      </c>
       <c r="M26">
         <v>-7.1</v>
       </c>
-      <c r="O26" s="2"/>
       <c r="P26">
-        <v>39.600752087373301</v>
+        <v>39.6007520873733</v>
       </c>
     </row>
   </sheetData>
